--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -445,10 +445,797 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>큐텐상품번호</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>상점ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>상품명(원본)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>한글검증명칭</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>가격(엔)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>옵션있음</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>카테고리코드</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1203566602</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>vanguardvista</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[正規品1+1] ヒートアクティブ極損傷傷つけるトリートメント 220ml+220ml</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ケラシス</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2891</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203566602</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1031781330</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gugumile</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[5枚] ナンバーズイン 4番 SOS急速冷却シートマスク, 27g*5 マスクシート</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ナンバーズイン</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1572</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1031781330</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>997222280</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gugumile</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ビフィダ バイオーム コンセントレート クリーム50ml/韓国化粧品/スキンケア/クリーム</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>manyo</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3465</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=997222280</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1141816688</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JDKM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>トーンアップ ホワイト マッド マスク 3個入り x 2個</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>バイアウア</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5214</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141816688</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1141816327</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JDKM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>わさびスージングマスク 30g</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Miss Dragon</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5709</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141816327</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1191488311</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hmipo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>アクアティカ サンスプレー 100mL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>セルフュージョンC</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191488311</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1206876054</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NARShA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[ブラシ元祖] グロウターンエクソソームブラシアンプル130ml企画(+30ml)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lily eve</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5950</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206876054</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1049588733</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>modeling</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>スーパーヴォルカニックポアクレイマスク2X, 100mL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>イニスフリー</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2090</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1049588733</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1204156842</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>modeling</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[1+1] トン＆スポット コレクターアンプル 30ml +30ml</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Redence</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>4620</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204156842</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1186174034</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>modeling</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[1+1]アルガンオイルダメージトリートメント300ml+300ml</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>エラスティン</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1186174034</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1156719535</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>modeling</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ソウルシークレットブロッサム香水30ml</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ザフェイスショップ</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1156719535</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1138185679</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JfromKorea</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>エアリー サンスティック スムージング バー 23g</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>アビブ</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2591</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1138185679</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1187136865</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JfromKorea</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>リアルミルク クレンジングフォーム 肌保湿 弾力 肌のキメ 水分改善150ml1本</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ブランカウ</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2863</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1187136865</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1177838255</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JfromKorea</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ハニーアンドマカダミア ネイチャーシャンプー ブラックベリーベイ 500ml</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kundal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1177838255</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1203234617</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PrincessRamen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>フォトデルム X-ディフェンス ウルトラ フルイド SPF50+ 40ml</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ビオデルマ</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4571</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203234617</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1079657711</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PrincessRamen</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>トリデン Torriden dive in 低分子 ヒアルロン酸 トナー 300ml/ダイブイントナー 300mL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>トリデン</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1079657711</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1210384893</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PrincessRamen</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ブルー ペプチド バクチオール プランプ バウンス クリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COSRX</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4428</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210384893</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1207603847</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PrincessRamen</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>メイクアップ フィクサー 80ml</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ヘラ</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4570</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207603847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:J19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1234,8 +1234,828 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1194335884</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OneulPick</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ハイミッシュ マリンケア アイクリーム 30ml (e)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ヘイミッシュ</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2196</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194335884</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1210847470</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OneulPick</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>id PLACOSMETICS リアルアフターケアミスト 120ml</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>id PLACOSMETICS</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3481</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210847470</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1194335721</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OneulPick</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>タイムレボリューションプライムステム100クリーム50ml</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ミシャ</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>4033</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194335721</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1209978694</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>OneulPick</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ワンレイヤートーンアップボディミスト100ml</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>KAHI</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2495</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209978694</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1138225289</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>dreamus</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>シグネチャーパルファム, 50ml, 1個</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FORMENT</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>5517</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1138225289</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1075323842</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>kosmetic</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>THE ORDINARY Alpha Arbutin 2% + HA [KOR] - 30ml</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ザ ヨン</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3210</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1075323842</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1075016731</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>kosmetic</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>韓国コスメ 肌の保湿The Niacinamide 15 Serum 20ml</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>COSRX</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2612</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1075016731</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1072484408</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HAMAHAMA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ダブルユードレスルームドレスパフュームNo.49ピーチブロッサム160ml</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>W.DRESSROOM</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1072484408</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1115880952</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HAMAHAMA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ノースカナイントラブルセラム 30ml</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>パティオン</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>4260</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1115880952</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1072009140</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KOR--STORE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>バイオ スキン クレンジング パッド 6g 30枚入 x 2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>EKE</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1072009140</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1083261277</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KOR--STORE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CELL LINE PRO リペアクリーム [100口] 半永久化粧材料 アフターケア 1g100個入り</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Clear_pro</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1083261277</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1209979406</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>onnicosme</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>【正規品】ハンーユル 幼いヨモギ 皮脂吸着 ヨモギ餅パックフォーム 120ml, 1個</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ハンユル</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3450</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209979406</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1204386062</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>onnicosme</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>【正規品】朝鮮の美女 人参アイクリーム 30ml（ビタミンA レチナール リポソーム）</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2890</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204386062</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1203715344</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>onnicosme</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>【正規品】 フォア パーフェクティング コラーゲン ペプチド クリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Biodance</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>4190</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203715344</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1202714464</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>onnicosme</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>【正規品】 マデカーメラキャプチャーアンプルパッド60枚x2個</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3890</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202714464</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1204254720</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>k-pick72811</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[ウォーターミストプランピング][正規品] マダガスカル センテラ ヒアル-テカ プランピング アンプル 50ml／スキンブースティング／ヒアルプラム</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>5743</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204254720</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1199087370</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>k-pick72811</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[和解1位/脱毛シャンプー] パープルブースター [正規品]玉ねぎシャンプー/紫の抗酸化ブースター</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>prooted</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>5990</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199087370</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1167124675</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TwoK</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ラエル オーガニックコットンカバー 履くオーバーナイト M 2個入 x3個</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ラエル</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>3059</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1167124675</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1202040262</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TwoK</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ジョソンアビューティ ワンダーバス レモンシロップ パッククレンザー 200ml (+50ml)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WONDER BATH</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>4332</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202040262</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1202040223</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TwoK</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>エストラ エイシカ365 スーディング リペア マスク pH4.5 5枚</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AESTURA</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>4378</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202040223</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2054,8 +2054,623 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1193633283</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>REALBEAUTYSHOP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BRING GREEN 公式 ブリングリーン ティーツリーシカディープ洗顔フォーム 120ml+120ml BRINGGREEN 洗顔 クレンジング</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193633283</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1193632664</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>REALBEAUTYSHOP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BRING GREEN 公式 ブリングリーン ティーツリーＣ トナー 500ml BRINGGREEN 化粧水</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>4490</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193632664</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1193632481</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>REALBEAUTYSHOP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BRING GREEN 公式 ブリングリーン ティーツリーシカセンシティブクレンジングウォーター 500ml BRINGGREEN 洗顔 クレンジング</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2990</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193632481</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1193834160</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KBEAUTYOFFICIALSTORE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BRINGGREEN 公式 ブリングリーン ティーツリーシカセンシティブクレンジングウォーター 500ml BRINGGREEN 洗顔 クレンジング</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2990</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193834160</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1190361804</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KBEAUTYOFFICIALSTORE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>【大容量 100ml】 CNP Laboratory 公式 プロポリス エネルギー アクティブ アンプル 50ml+50ml cnp 美容液 プロp セラム プロポリス エネルギーアンプル</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CNP Laboratory</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>7880</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190361804</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1191474301</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>KBEAUTYOFFICIALSTORE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>REJURAN 公式 リジュラン PDRN (c-PDRN) ポアタイトニングトナーパッド 60枚 トナーパッド パック</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>リジュラン</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>4490</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191474301</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1193841835</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Oliveofficial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Celimax 公式 セリマックス レチナール タイトニング ブースター 15ml+15ml THE ビタA レチノールショット タイトニングブースター</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>7990</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193841835</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1171441772</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Oliveofficial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BRING GREEN 公式 ブリングリーン ティーツリーＣ トナー 500ml BRINGGREEN 化粧水</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>4490</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171441772</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1165725748</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>yoo_k1120</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[正規品/K-Beauty] アイドル ホワイト タンニング スプレー 150ml</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DODO LABLE</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>5070</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1165725748</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1193635878</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>chaudmaison</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMPLE:N 公式 アンプルエヌ ペプチドショット アンプル 2X 100ml ペプチドショット 2X アンプルn 美容液</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>アンプルエヌ</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>4490</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193635878</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1171450184</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>chaudmaison</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BRING GREENブリングリーン 公式 ティーツリーシカディープ洗顔フォーム 120ml+120ml BRINGGREEN 洗顔 クレンジング</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171450184</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1171450008</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>chaudmaison</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BRING GREENブリングリーン 公式 ブリングリーン ティーツリーＣクリーム100ml+100ml BRINGGREEN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>4390</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171450008</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1188402180</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EGF ポストレーザー セラムミスト 120ml [再生+鎮静+ミスト]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>イージーデュー</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>5130</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188402180</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1188402173</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>アロエ スージングジェルミスト 155ml×3 [鎮静+保湿+時短]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ネイチャーリパブリック</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2940</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188402173</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1188402116</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ダーマアンサー PDRN アンプル 30ml+60ml リフィル [弾力+保湿+セット]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CNP Laboratory</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5410</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188402116</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J39"/>
+  <autoFilter ref="A1:J54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2669,8 +2669,541 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1131417905</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>beautybarseoul</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>化粧水 ブレミッシュケアトニックエッセンス130ml</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>アイソイ</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2943</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1131417905</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1207189650</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>beautybarseoul</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ライスブライトニングパッド60枚(60pcs) 米</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>スキンフード</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2208</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207189650</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1203101387</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>beautybarseoul</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ホワイトトリュフエキソインテンシブセラム160ml 美容液ミスト</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>2583</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203101387</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1203100590</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>beautybarseoul</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ホワイトトリュフアクアマリンエネルギーセラム160ml blue mist</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2592</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203100590</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1180348228</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SOFS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ミストセラムホワイトトリュフインテンシブロイヤルセラム60ml</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1699</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180348228</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1180348010</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SOFS</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>コラーゲンコア水光マスク80ml</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ティルティル</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>3850</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180348010</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1203096775</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SOFS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>フィディアルエン(PDRN)毛穴タイトニングパッド(100pcs) リフティング</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>メディヒール</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>2691</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203096775</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1180349223</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SOFS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>マデカセンテラスーディングミスト100ml ツボクサ 鎮静スプレー</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2597</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180349223</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1210931751</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>glowhouse</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[単独企画] エンドポアベジチノール タイトニング 毛穴 セラム 50ml (+インティカクリーム31ml) / 韓国 人気 コスメ</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>メイクプレム</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>4540</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210931751</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1195070823</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>cosme_beauty</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>スネイルエッセンス 美容液 カタツムリローション 100mL カタツムリスネイルセラム保湿栄養エッセンス敏感肌乾燥肌カタツムリ粘液</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>COSRX</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1880</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1195070823</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1209257132</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>cosme_beauty</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>9番 NMN PDRNグロートリートメントトナー 150ml</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ナンバーズイン</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2080</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209257132</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1208957871</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>cosme_beauty</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>[1+1] サリチル酸 デイリー ジェントル クレンザー/Salicylic Acid Daily Gentle Cleanger 150ml + 150ml</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>COSRX</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208957871</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1199834618</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>bestkoreanitems</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EMS 振動リフトクレンザーヘッド</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>7690</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199834618</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J54"/>
+  <autoFilter ref="A1:J67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3202,8 +3202,582 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1210946100</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Yeonbunong</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>オリーブヤング プレステージ ローション トゥエックス ジンセン デスカルゴ 140ml</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>イッツスキン</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>4460</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210946100</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1210829091</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Yeonbunong</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>オリーブヤング ドクターセイバス セラムマスク PDRN 10枚</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>イッツスキン</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2310</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210829091</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1208091250</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Yeonbunong</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>シグニチャー バイオ ディープ コラーゲン ファーミング マスク パック 12枚入り リフトアップ フェイスパック 韓国コスメ　コラーゲン　ハリ</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>VINNE</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>14500</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208091250</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1199482761</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Yeonbunong</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>[栄養] オリーブヤング 大豆エッセンス 50ml</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ミクスン</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>4570</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199482761</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1208332251</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>hanamiselect</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>【正規品】ライスアクアフレッシュサンクリーム 50ml SPF50+ PA++++ 日焼け止め</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>2190</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208332251</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1208994497</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>hanamiselect</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>【正規品】白樺ミネラルサンクリーム SPF50+ PA++++ 50ml</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208994497</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1132391030</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>hanimall</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>アトバリア 365 クリーム 80ml</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AESTURA</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>4510</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1132391030</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1146402210</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>hanimall</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>シラカバ 水分 サンクッション 15g</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>3080</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1146402210</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1133988984</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hanimall</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>センテッド ハンドクリーム 40ml/韓国化粧品/パフュームハンドクリーム</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>hince</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1133988984</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1211674770</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KORESHOP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ディープダメージリペアシャンプー 500ml + 詰め替え 400ml 大容量セット スイートブリーズの香り</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>UNOVE</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>4247</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211674770</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1203834476</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>KORESHOP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>白樺水分サンクッション 15g</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203834476</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1193418611</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KVIVE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ヒーラー ポア タイトニング トナーパッド 本品60枚+詰め替え用 60枚入り/PDRN トナーパッド 美容液 /韓国 人気 トナーパッド/弾力/保湿/水分アンプル/c-PDRN/エイジングケアトナー</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>リジュラン</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>6870</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193418611</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1202579985</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>KVIVE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>[1+1] 選べるサンセラム 2個セット (水分鎮静 / 弾力トーンアップ) SPF50+ PA++++/マデカソサイド 鎮静 or PDRN トーンアップ サンセラム / 美容液 日焼けめ</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>メディヒール</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>4890</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202579985</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1207120098</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LUNORASELECT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>マスターズ エアリッチ サンスティック 22g 2個 セット ポケモン エディション 日焼け止め UVカット 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AHC</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>4836</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207120098</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J67"/>
+  <autoFilter ref="A1:J81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3776,8 +3776,623 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1206006286</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ALLisWELL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ローズオブセッション ティント 24種（グロウ/マット）</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>フィー</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1831</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206006286</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1197650165</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ALLisWELL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EFGセサル軟膏 5g / EGFクリーム (保湿ケア / 敏感肌サポート)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>大熊製薬</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>2548</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197650165</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1194294476</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>myoneshop</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>[マグネティックネイル] マジックプレス グロウベリー（アーモンド）ネイルチップセット 1個</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ダッシングディバ</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>4829</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194294476</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1171937523</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>myoneshop</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>[キンモクセイの香りエディション] ハニーアンドマカダミア ネイチャーパフュームシャンプー400ml×1個+トリートメント400ml×1個+GIFTシャンプーブラシ</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Kundal</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>5990</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171937523</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1134929906</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>myoneshop</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>[韓国マスクパックセット]ダイブイン低分子ヒアルロン酸マスク6枚+メディヒールマデカソサイドエッセンシャルマスク11枚+GIFTナンバーズイン2番ビューティーコラーゲンボリュープマスク1枚</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>トリデン</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>6299</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1134929906</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1207547885</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>kim701016</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>メラノサクリーム 30g</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>東亜製薬</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207547885</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1204931350</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>kim701016</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>スーパー ドロップス - ビタC トーニング セラム 大容量バナナキック エディション</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ビリーフ</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>4050</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204931350</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1204628544</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>kim701016</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ハウス・オブ・ビ・グルタチオン・フェイスフィルム（3+1）</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>HOUSE OF B</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204628544</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1203899937</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>kim701016</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>レッドサクセニックアシッドパッド/ ニキビ跡・角質ケア・毛穴汚れ / 低刺激・拭き取り化粧水</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="b">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203899937</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1203826917</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>kim701016</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ヒアルロン酸水分カプセルクリーム 55g/インナードライ・保湿・ツヤ肌 / 低刺激・水分補給</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>3960</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="b">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203826917</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1191781202</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>A-RAUM</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MEDIHEAL トナーパッド2.0 リフィル 70枚×2個セット 4タイプ選択可</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>メディピール</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1918</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="b">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191781202</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1204359324</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A-RAUM</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>【1+1 / SNS話題】ツヤ肌バブルエッセンストナー 95ml</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>curest</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2131</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="b">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204359324</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1120129564</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ikoniko</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ヘアロールブラシ(Big,58mm)ヘアスタイリング</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>HAUM</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>4475</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1120129564</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1151670543</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>KORKORMALL</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[国内百貨店]ディープディックフレッドポッドボディバーム200ml</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ディプティック</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1151670543</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1151671051</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>KORKORMALL</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>【国内百貨店】ルラボベルガモット22オードパルファム15ml</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>LE LABO</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>19280</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1151671051</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J81"/>
+  <autoFilter ref="A1:J96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4391,8 +4391,664 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1204368140</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CosmeticsNo1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ラディアンソーム100マイクロフルーダイザトナー＋エッセンス</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="b">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204368140</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1212645182</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CosmeticsNo1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[1+1+1]ボルフィリン 20% アンプルスティック 10ml x 3EA</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Derma Factory</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212645182</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1212154060</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CosmeticsNo1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[1+1+1]トラネキサム酸6%クリーム, 30ml x 3EA</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Derma Factory</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="b">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212154060</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1212147421</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CosmeticsNo1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>[1+1]トラネキサム酸6%クリーム, 30ml x 2EA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Derma Factory</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="b">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212147421</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1199006617</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Jurian</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>アゼライン酸16BBカーミングセラム, 30ml</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>2578</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="b">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199006617</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1199701690</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Jurian</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>カーミング バランスジェル 100ml / 水分バランス 調節</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>4735</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199701690</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1192507748</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>megadepartment</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>[国内発送]超低分子ヒアルロン酸トナー300ml/オニオンニューペアゲルクリーム50ml/ヒアルロン酸化粧水 ヒアルロン酸トナー/水分 保湿 潤い 乾燥肌 混合肌/韓国コスメ 韓国スキンケア[選択]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>イズエンツリー</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3</v>
+      </c>
+      <c r="H103" t="b">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1192507748</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1202278739</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>megadepartment</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>THE VITA A PDRN レチナールショット タイトニングブースター 20g / PDRN レチナール スポットクリーム / ハリ 弾力ケア 毛穴ケア シワ改善 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MABUP YEOSHIN</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="b">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202278739</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1210416288</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>coscoskorea</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>カーミングバランスジェル 100ml</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>4990</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="b">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210416288</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1210395714</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>coscoskorea</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>クレンジングパウダーウォッシュ 80g</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>4490</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="b">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210395714</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1210367966</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>coscoskorea</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ツーフェイスオイルミスト 50ml</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="b">
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210367966</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1064699032</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>hy_international</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ウォータープルーフプロサンクリーム50g SPF50+ PA++++</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BUSHMAN</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>2599</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1064699032</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1076432453</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>hy_international</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ヘアクッション 15g x 2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>lala chuu</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>3599</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" t="b">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1076432453</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1194137779</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>COSNRM</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>プラセン マジックシステム セット 1剤 / 2剤 200ml / 2種 1択</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ルネセル</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>7058</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="b">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194137779</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1194137521</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>COSNRM</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ルティナー マルチバーム 15ml 2個</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>aXENDA</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>8018</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="b">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194137521</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1172240115</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>COSNRM</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ダーマジェン イジェンシア 25g 2個 / 50g 2個 / 2種 1択 / 肌の回復と鎮静をサポートする集中保湿クリーム</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Dermagen</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>3956</v>
+      </c>
+      <c r="G112" t="n">
+        <v>6</v>
+      </c>
+      <c r="H112" t="b">
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1172240115</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J96"/>
+  <autoFilter ref="A1:J112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5047,8 +5047,664 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1179913892</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>KOREAHUB</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>マミケア ビビリップ LED リップ グロウ リップマスク 1個ケースリップバーム 2種乾電池</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Mommy Care</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>7420</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="b">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179913892</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1180095461</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>KOREAHUB</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>イーロン アンプル 50ml センシエンド</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ILLON</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>15970</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="b">
+        <v>0</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180095461</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1180095290</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KOREAHUB</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>イーロン ダンギ クレンジングジェル 200ml + 贈呈:マスクパック1枚</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ILLON</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>6550</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="b">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180095290</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1171638753</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UKB</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ソウル 1988 セラム: レチナール リポソーム 2% + ブラックジンセン 30ml</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>K-SECRET</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="b">
+        <v>0</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171638753</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1168676299</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UKB</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>モイスチャー·レイヤ·サン·プロテクター50ml SPF50+ PA++++</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>3995</v>
+      </c>
+      <c r="G117" t="n">
+        <v>9</v>
+      </c>
+      <c r="H117" t="b">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1168676299</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1187961763</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>heyyou</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>[2026] NEW 最低特典カーミング バランスジェル-保湿 / 鎮静 100ml(1+1)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>10057</v>
+      </c>
+      <c r="G118" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" t="b">
+        <v>0</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1187961763</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1174936338</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>heyyou</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>プリジュビネーション ファーミングバクチオールセラム[童顔弾力セラム] 50ml</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Dr.Jart+</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>6902</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="b">
+        <v>0</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1174936338</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1208171928</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>heyyou</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>[2026BEST] ザマトロジー 2種 セット-光彩 / 弾力(ブースター130ml+セラム45ml)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>13046</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="b">
+        <v>0</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208171928</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1210644303</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>on_j4052</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>【NEW】SW19 ヘアパフュームミスト 75ml 5pm 8am 2種から選べる1種 ヘアミスト ヘアフレグランス 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>SW19</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>5490</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="b">
+        <v>0</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210644303</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1210988490</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>[正規品] SET VQM Phytocin VIBANQM LOTION 30ml + フィニッシュローション20ml</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>CONAPIDIL</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>11780</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="b">
+        <v>0</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210988490</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1212008071</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>[正規品] ナチュラル毛穴カバー乳液 韓国正規品</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>オブジェ</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>3070</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="b">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212008071</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1211131806</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>[公式販売店] ザマトロジー 2種セット[ブースター+セラム]/韓国化粧品</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>11970</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="b">
+        <v>0</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211131806</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1211312549</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>[公式販売店] 【1+1】 低刺激ディープクレンジング モイスチャー クレンジングオイル 145ml</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>7790</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="b">
+        <v>0</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211312549</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1211131359</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>[公式販売店] ICD 3種 ラジアンソーム100トナー/クリーム/エッセンス</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>29990</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="b">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211131359</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1177131836</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>koreahubshop</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ドクターヘディソンピュア100％ビタミンCパウダー50gアンプルトナービタケア</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Dr. Hedison</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>4560</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="b">
+        <v>0</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1177131836</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1189937314</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>koreahubshop</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>アノブ ディープ ダメージ リペア シャンプー 1 + 1 ダブルセット 500ml+500ml</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>UNOVE</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>4840</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="b">
+        <v>0</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189937314</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J112"/>
+  <autoFilter ref="A1:J128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5703,8 +5703,541 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1189781351</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>YOUSTUDIO</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ブライタミン V7トーニング ライトクリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Dr.Jart+</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>5299</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="b">
+        <v>0</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189781351</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1196020481</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NDY</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ツーフェイス オイルミスト 50ml 1個 基礎化粧品 保湿 潤い 艶肌 油水分バランス [並行輸入品]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>4980</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2</v>
+      </c>
+      <c r="H130" t="b">
+        <v>0</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1196020481</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1208338165</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>AnchorBlue</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>[サロン級ホームケア] エクストリーム ダメージ クリニック ヘア アンプル 10ml 9個入り / 傷んだ髪 高濃縮 補修 保湿 ツヤ髪 トリートメント 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ケラシス</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>3818</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="b">
+        <v>0</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208338165</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1209905054</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>hiseller</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ホワイトアプリコット ソリッドパフューム 塗る固体香水 フレグランス 携帯用 30ml</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LUAFEE</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>2499</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="b">
+        <v>0</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209905054</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1209905260</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>hiseller</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>オドール オールインワン クリアボディウォッシュ 2個, 460ml</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Nodor</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>7665</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="b">
+        <v>0</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209905260</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1209905066</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>hiseller</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ポケモンエディションクリアボディミスト 200ml 企画 (ミニチュア 30ml + イーブイ防水パック)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>NOT4U</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>3831</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="b">
+        <v>0</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209905066</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1208411222</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>keto88</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ブラーフィニッシュサンクッション,リフィル</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>TOCOBO</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1880</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="b">
+        <v>0</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208411222</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1173120891</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>vivienpink_SG_jp</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>魔女工場 ピュア クレンジングティッシュ</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>manyo</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>2090</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="b">
+        <v>0</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1173120891</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1174362545</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>vivienpink_SG_jp</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ブライトニング毛穴ジャブティパッド本品40枚+10枚（追加贈呈）</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>3890</v>
+      </c>
+      <c r="G137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H137" t="b">
+        <v>0</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1174362545</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1201547339</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RARI</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>パフュームハンドクリーム [ハローキティ], 50ml</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ヘトラス</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>2170</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="b">
+        <v>0</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201547339</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1158151170</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>royalshop</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>【NEW】 ドクダミ センテラ レッドスポット クリーム 韓国コスメ 30g</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>2824</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4</v>
+      </c>
+      <c r="H139" t="b">
+        <v>0</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1158151170</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1155003250</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>royalshop</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>つや米 トーンアップ 水分 サンクリーム 日焼け止め 化粧下地 UVカット SPF50+ PA++++ 韓国コスメ [ロイヤルショップ] 100mL</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>シンムルナラ</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>3413</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="b">
+        <v>0</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1155003250</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1157009011</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>royalshop</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>エアライン KF94 黄砂・飛沫対策 3Dマスク 大型サイズ 韓国マスク 100枚セット（25枚×4袋）［ホワイト/ブラック］</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>URBANWIZ</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>2477</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="b">
+        <v>0</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1157009011</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J128"/>
+  <autoFilter ref="A1:J141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6236,8 +6236,418 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1207716735</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>sowoojushop</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ハニー＆マカダミア ピュアボディローション アカシアモリンガの香り 500ml 韓国ボディケア 保湿ケア しっとり ボディミルク</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Kundal</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>2705</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="b">
+        <v>0</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207716735</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1163853917</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>theonetrade</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>緊急鎮静・敏感肌ケア / 韓国スパ品質の陶器肌クリーム P401 リリーフクリーム 50mL</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Eclat du teint</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>9900</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="b">
+        <v>0</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163853917</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1149797233</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>theonetrade</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>韓国発の人気商品 SW19 ミニ香水お試しセット 3mL X 4本セット</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>SW19</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2</v>
+      </c>
+      <c r="H144" t="b">
+        <v>0</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1149797233</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1149301635</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>theonetrade</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>韓国で人気のスキンケア5点セットRENEW-AGE スキンケアトナー130mL + 乳液130mL + 美容液30mL + クリーム50mL + アイクリーム20mL ギフトとしても大人気</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AHC</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="b">
+        <v>0</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1149301635</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>934718142</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>theonetrade</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>トラブルソープドクダミ石鹸 手作り石鹸100g 1+1/ニキビケア/皮脂コントロール/優しい使い心地/韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>LANOA</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>3999</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="b">
+        <v>0</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=934718142</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1120312659</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>kinakomall</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Glycolic Acid 7% Exfoliating Toner グリコリックアシッド7%エクスポリエイティングトナー(Toning Solution) 100ml, 240ml / グリコリック</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>ジオーディナリー</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1789</v>
+      </c>
+      <c r="G147" t="n">
+        <v>8</v>
+      </c>
+      <c r="H147" t="b">
+        <v>0</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1120312659</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1193462376</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>kinakomall</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ベータグルカン パワーモイスチャーセラム 50ml</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>iUNIK</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>3408</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="b">
+        <v>0</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193462376</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1211134600</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>seimyongkorea</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>【NEW】 シェイキングミスト</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>フィー</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>2222</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="b">
+        <v>0</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211134600</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1197720706</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>K_Beauty_Station</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>【今だけ限定！企画】キャロットカロテンカーミングウォーターパッド, 60枚</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>スキンフード</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1964</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3</v>
+      </c>
+      <c r="H150" t="b">
+        <v>0</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197720706</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1212963285</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>K_Beauty_Station</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ドクダミBHA ジウゲ ピーリングパッド 70枚(60+10枚) 毛穴ケア 角質ケア 皮脂ケア</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1764</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="b">
+        <v>0</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212963285</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J141"/>
+  <autoFilter ref="A1:J151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6646,8 +6646,705 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1212713877</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Lulupi</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>【フィー】 シェイキングシナジーミスト 50ml 全3種</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>フィー</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>2654</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="b">
+        <v>0</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212713877</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1213885966</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Lulupi</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>【ソーナチュラル】 オールデイ ブラー ジェリー プライマー フィクサー 5g</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>ソーナチュラル</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>2432</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="b">
+        <v>0</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213885966</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1180144570</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>yeppun</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>PDRN トナー250ml1個</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>3230</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="b">
+        <v>0</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180144570</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1202055978</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>yeppun</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>UVクリーム SPF50+ PA ++++ 敏感肌向けトーンアップ韓国コスメの人気日焼け止め</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AESTURA</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>4370</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="b">
+        <v>0</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202055978</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1174315936</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>yeppun</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>1. マデカラボ マスク 10枚×2箱（リンクル リバイタライズ）</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="b">
+        <v>0</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1174315936</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1183743968</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>zz6o6</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>パーフェクト9 インテンシブ スキンケアセット 化粧水 乳液 クリーム セット スキンケア 保湿 セット 保湿</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>イニスフリー</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>5253</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="b">
+        <v>0</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1183743968</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1177458353</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>zz6o6</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>コジサン ソープ 65g×3個 フィリピン製 ナチュラル オレンジ石鹸 ギフトにもおすすめ</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>こじえさん</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>2232</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="b">
+        <v>0</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1177458353</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1103721247</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>COREDREAM</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Inner perfume 5ml 14種 / Yゾーンケア /生臭さ除去 / 下着香水</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>フォエリー</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>2190</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3</v>
+      </c>
+      <c r="H159" t="b">
+        <v>0</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1103721247</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1191723236</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>treasurebeauty</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ホワイトティ ジンジャーリリー ボディクリーム 400ml</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>エリザベスアーデン</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>3344</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="b">
+        <v>0</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191723236</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1203745241</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>treasurebeauty</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>スキンコンディショナーエッセンシャル 330ml</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>アルビオン</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>10106</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="b">
+        <v>0</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203745241</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1154890233</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>bettysbeauty</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ロム イデアル インテンス オーデパルファン 100ml</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>ゲラン</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>20617</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="b">
+        <v>0</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1154890233</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1123998991</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>bettysbeauty</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>イリシットオーデパルファム 100ml</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>ジミーチュウ</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>10654</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="b">
+        <v>0</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1123998991</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1163881732</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>bellcosme</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ロレアル セリエ ブロンディファイアー マスク 500ml</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>LOREAL PARIS</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>5374</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="b">
+        <v>0</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163881732</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1123944887</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>bellcosme</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>グリーンティー ボディローション 500ml</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>エリザベスアーデン</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>1679</v>
+      </c>
+      <c r="G165" t="n">
+        <v>7</v>
+      </c>
+      <c r="H165" t="b">
+        <v>0</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1123944887</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1204380898</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>bellcosme</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ニューバーム ソフトムスク 40g</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>RETOUCH</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>2809</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="b">
+        <v>0</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204380898</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1189355281</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>beautyofkorea</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ドクダミ77％ 化粧水 250ml</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>1761</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="b">
+        <v>0</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189355281</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1131933510</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>K-Aesthetique</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>セルマン ビタミンC セラム 30ml Vitamin C Serum エステサロン専用 韓国化粧品</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>SERMENT</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>8300</v>
+      </c>
+      <c r="G168" t="n">
+        <v>5</v>
+      </c>
+      <c r="H168" t="b">
+        <v>0</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1131933510</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J151"/>
+  <autoFilter ref="A1:J168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7343,8 +7343,746 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1197392833</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>KOKOkr</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PDRNデイリーマスク 30枚</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>1599</v>
+      </c>
+      <c r="G169" t="n">
+        <v>7</v>
+      </c>
+      <c r="H169" t="b">
+        <v>0</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197392833</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1196376380</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>KOKOkr</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>マダガスカルセンテラヒアル-シカシルキーフィットサンスティック 20g SPF50+ PA++++</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>1599</v>
+      </c>
+      <c r="G170" t="n">
+        <v>8</v>
+      </c>
+      <c r="H170" t="b">
+        <v>0</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1196376380</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1172550313</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>KOKOkr</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PDRNピンクペプチドアンプルリフィル50ml / 1個</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>1649</v>
+      </c>
+      <c r="G171" t="n">
+        <v>4</v>
+      </c>
+      <c r="H171" t="b">
+        <v>0</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1172550313</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1157524219</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>KLand</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>バイオEXセルペプチド3種セット1個 水分・保湿・栄養・肌のハリ・シワケア</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>トニーモリー</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>5979</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="b">
+        <v>0</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1157524219</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1149796005</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>KLand</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>センテラ トーニングトナー 鎮静 シカ 化粧水 210ml</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>1974</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="b">
+        <v>0</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1149796005</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1172781112</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>KLand</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>[3点セット/企画構成/復活草マスクパック1枚贈呈]復活草 パハトナー200ml+復活草 ビフィダ セラム ファーミング ドロップ 50ml+復活草 クリーム ニュートリション チューブ 75ml</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>アビブ</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>5819</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="b">
+        <v>0</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1172781112</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1155298751</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>KLand</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>【リニューアル】ゼロ毛穴 ワンデーセラム 30ml 1本 毛穴ケア 肌のキメ</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>2348</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="b">
+        <v>0</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1155298751</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1151012307</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>KLand</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ドクダミポアコントロールクレンジングオイル 200ml</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>2691</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="b">
+        <v>0</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1151012307</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1163428866</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>kspecial</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>キュスカゲル 10g ビタミンE 配合 ステロイド無添加 ケロイド 肥厚性瘢痕 ニキビ跡医療用シリコンゲル 手術・火傷・外傷 傷跡管理</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>セラディックス</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="b">
+        <v>0</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163428866</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1162958747</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>topkorea</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>リアルマットメイクアップセッティングフィックスミスト75ml フィクサー メイクキープミスト メイクキープスプレー /韓国コスメ 韓国スキンケア</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>ソーナチュラル</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G178" t="n">
+        <v>6</v>
+      </c>
+      <c r="H178" t="b">
+        <v>0</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1162958747</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1083980822</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>topkorea</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>セラミドアト6.0 トップトゥトー全身ウォッシュ 1000ml</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>イリユン</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>2732</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="b">
+        <v>0</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1083980822</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1167024145</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>topkorea</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ホワイトトリュフファーストスプレーセラム 100ml /150ml 保湿/栄養/弾力/ハリ/光彩/ツヤ/</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>2090</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="b">
+        <v>0</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1167024145</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1162947006</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>topkorea</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ガラクナイアシン3.0エッセンス, 60ml, /韓国コスメ 韓国スキンケア</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>manyo</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G181" t="n">
+        <v>4</v>
+      </c>
+      <c r="H181" t="b">
+        <v>0</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1162947006</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1209235398</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Oningvibe</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>エクソソーム保湿クリーム 50ml 韓国コスメ 韓国ブランド 公式ショップ 韓国スキンケア スキンケア 化粧品 敏感肌 乾燥肌 水分ケア うるおい 韓国アンプル ギフト PDRN CICA</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Oningvibe</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>2664</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="b">
+        <v>0</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209235398</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1209222941</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Oningvibe</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>エクソソーム保湿トナー 150ml 韓国スキンケア 韓国コスメ スキンケア PDRN CICA ヒアルロン酸 水分ケア　乾燥肌 ローション 化粧水 整肌成分 毎日のケア 弱酸性 韓国商品 高保湿</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Oningvibe</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>2472</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="b">
+        <v>0</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209222941</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1210318709</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Oningvibe</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>エクソソーム保湿アンプル 30ml 2個セット 1+1 美容液 セラム 韓国コスメ 韓国スキンケア 化粧品 スキンケア PDRN パインショットエクソソーム CICA うるおい 水分 アンプル</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Oningvibe</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>3336</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="b">
+        <v>0</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210318709</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1209368965</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Oningvibe</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>エクソソーム保湿パッククレンザー 150ml 洗顔 メイク落とし 乾燥肌 敏感肌 弱酸性 韓国スキンケア 韓国コスメ クレンジング 保湿 泡立ち 2WAY パック 韓国化粧品 韓国 韓国好き</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Oningvibe</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>2454</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="b">
+        <v>0</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209368965</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1190410398</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>lebelage</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>【公式】【1つ選択】トゥルーリートナーパッドシリーズ5種（各60枚入り）／拭き取りパッド／部分パック／肌悩み別トナーパッド／グルタチオン／パンテノール／センテラ／レチノール／時短ケア</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>ルベラジュ</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1710</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="b">
+        <v>0</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190410398</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J168"/>
+  <autoFilter ref="A1:J186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8081,8 +8081,172 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1168425085</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>lannor</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ザマデカクリーム (シーズン6), 50ml, 3個 (ボックス無)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>2752</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="b">
+        <v>0</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1168425085</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1151142091</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>vacian</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>【公式】ゴールドシル ペプチド コラーゲン シワ リフティング アンプル 30mlハリ肌・エイジングケア・韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>VACIAN</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="b">
+        <v>0</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1151142091</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1140049631</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>vacian</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>【公式】 目元リフティング スピキュール ペプチド アイクリーム 15ml たるみ・シワ・エイジングケア・韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>VACIAN</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="b">
+        <v>0</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1140049631</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1183673001</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>t-garden</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>【OUTLET】 シースルーグロス 【COOL】【WARM】シャンプー / トリートメント ボトル</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>RASICA</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>1584</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="b">
+        <v>0</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1183673001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J186"/>
+  <autoFilter ref="A1:J190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J190"/>
+  <dimension ref="A1:J204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8245,8 +8245,582 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1165888568</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>camihouse</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>[韓国公式] [1+1] 2個セットピックミ ーソーホットスリーミングボディジェル180ml / 二腕 / マッサージクリーム / 温熱クリーム / セルライト / アロエベラ</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>lovelycc</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G191" t="n">
+        <v>5</v>
+      </c>
+      <c r="H191" t="b">
+        <v>0</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1165888568</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1122868138</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>hibeautyland</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>PDRNピンクシカスージングトナー, 250ml</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>1937</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" t="b">
+        <v>0</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1122868138</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1131995829</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>hibeautyland</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>5番 白玉グルタチオン100xTXA10集中トーニング美容液, 2個</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>ナンバーズイン</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>3290</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" t="b">
+        <v>0</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1131995829</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1131788387</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>hibeautyland</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>コウジ酸ビタナイアシンアミドセラム, 30ml</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="b">
+        <v>0</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1131788387</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1190401836</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>lucylucy</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>【脱色/染め 5回分】イージーブロウ チェンジャー 5回分 / 01 トーンチェンジャー / 02 ムードチェンジャー / 眉毛染め / 眉毛脱色 / アイブロウカラー</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>コスノリ</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G195" t="n">
+        <v>4</v>
+      </c>
+      <c r="H195" t="b">
+        <v>0</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190401836</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1191967561</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>lucylucy</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>【knock,】メルトイン ボディトナー 300ml 4種の香り / ボディミスト ボディローション ボディケア</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>ノック</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>5150</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="b">
+        <v>0</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191967561</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1213260157</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SMILESCOOP</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ディアボーテ ブルームドール モイスチャー in シャンプー トリートメント ポンプ セット ひまわり ヒマワリ ヘアケア うねり くせ毛 パサつき 湿気 髪の体幹美容</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>ディアボーテ</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>2614</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="b">
+        <v>0</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213260157</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1205758834</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SMILESCOOP</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>【セット】NEXXUS(ネクサス) ケラフィックスリペア シャンプー+コンディショナー(トリートメント) 詰め替えペア 各320g おまけ付き</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ネクサス</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>2249</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="b">
+        <v>0</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205758834</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1202164401</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SMILESCOOP</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>TIMEU(タイムユー) T/MEU キープモイスト シェイキングミスト [ 洗い流さないトリートメント ] クリアフルールの香り 100ml</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>T/MEU</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>2112</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="b">
+        <v>0</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202164401</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1179799644</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>kitsunehouse</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>【正規品】[旧]センテリアンMDクリーム 80g / [新]マデカMDクリーム 80g / 韓国病院クリーム / 医療用 / レーザー後ケア / 敏感肌・超乾燥肌・混合肌用再生クリーム</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>2390</v>
+      </c>
+      <c r="G200" t="n">
+        <v>3</v>
+      </c>
+      <c r="H200" t="b">
+        <v>0</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179799644</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1203305204</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>sogokzip</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>neostrata ultra moisturizing face cream 40g</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ネオストラータ</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>7540</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="b">
+        <v>0</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203305204</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1197308524</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>sogokzip</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ronas tox volume cream 100ml</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>ronas</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>8200</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="b">
+        <v>0</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197308524</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1188906597</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>unain</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>コンセントレート シグネチャー クリーム ライト 84ea</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>HOLITUAL</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>3690</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="b">
+        <v>0</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188906597</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1171827286</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>unain</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>[ミニ 6セット]バウンシースリーピングマスク 60ml(10ml *6個)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>ラネージュ</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G204" t="n">
+        <v>7</v>
+      </c>
+      <c r="H204" t="b">
+        <v>0</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171827286</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J190"/>
+  <autoFilter ref="A1:J204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:J210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8819,8 +8819,254 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1044329808</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>baba442562</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>アクアスクワランモイスチャークリーム, 60ml, 30ml</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>エスネイチャー</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1640</v>
+      </c>
+      <c r="G205" t="n">
+        <v>9</v>
+      </c>
+      <c r="H205" t="b">
+        <v>0</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1044329808</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1037617271</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>baba442562</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>バイオコンディショニング エッセンス シートマスク20枚 (ボックス無) / フェイスパック</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>アイオペ</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G206" t="n">
+        <v>4</v>
+      </c>
+      <c r="H206" t="b">
+        <v>0</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1037617271</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1195466420</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>baba442562</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ザマデカクリーム (シーズン6), 50ml, 3個 (ボックス無)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="b">
+        <v>0</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1195466420</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>1212246885</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Mamiya</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>【 シャンプ600ml 1本+リンス600ml 1本】【パヒュームエレガンスアンバー】엘레강스 엠버향/ケラシス パフューム/合わせて2本セット/ELEGANCE AMBER/Kerasys</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>ケラシス</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="b">
+        <v>0</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212246885</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1209203301</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Mamiya</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>【シャンプー600ml * 3本+リンス600ml*3本】シャルマンマスクの香り/ケラシス パフューム/合わせて6本セット/CHARMANT MUSK/Kerasys</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ケラシス</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="b">
+        <v>0</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209203301</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1209860241</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>RomNsome</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>[NEW]オールデイ メイクアップ セッティング フィックス ミスト 75mlセット / メイクキープ / 崩れ防止 / メイクキープ</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ソーナチュラル</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="b">
+        <v>0</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209860241</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J204"/>
+  <autoFilter ref="A1:J210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$217</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J210"/>
+  <dimension ref="A1:J217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9065,8 +9065,295 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1146130861</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>_hiyu</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>[10+10] リアルネイチャー マスク シート 韓国 コスメ(ティーツリー/カモミール) 細かい毛穴/肌鎮静 デイリー ホームケア</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>ネイチャーリパブリック</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>2690</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="b">
+        <v>0</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1146130861</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1109317016</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>INFJA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>【最安値挑戦中】鎮静4種セット</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>11860</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3</v>
+      </c>
+      <c r="H212" t="b">
+        <v>0</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1109317016</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1092054474</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>INFJA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>【10枚】ナンバーズの4番SOS緊急鎮静氷場パック全10枚</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>ナンバーズイン</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>3860</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="b">
+        <v>0</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1092054474</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1199430782</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>charmang</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>[NEW]オールデイブラーメイクアップセッティングフィックスミスト75ml/ふんわり密着/メイクキープスプレー</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>ソーナチュラル</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G214" t="n">
+        <v>3</v>
+      </c>
+      <c r="H214" t="b">
+        <v>0</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199430782</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1168915716</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>charmang</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>【パックツール贈呈】プレミアムモデリングマスクパック1kg/石膏パック【10種】</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>LINDSAY</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>2869</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="b">
+        <v>0</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1168915716</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1133707312</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>charmang</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>【1+1】ダイブインセラム,100mL/ヒアルロン酸/水分/セラム</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>トリデン</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>4749</v>
+      </c>
+      <c r="G216" t="n">
+        <v>3</v>
+      </c>
+      <c r="H216" t="b">
+        <v>0</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1133707312</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1169961316</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>TOMOSONGSTORE</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>オードパルファム 100ml 甘美で神秘的なアロマが織りなすフェミニンで忘れられない香り</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>ロリータ レンピカ</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>8440</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" t="b">
+        <v>0</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169961316</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J210"/>
+  <autoFilter ref="A1:J217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J217"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9352,8 +9352,336 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1184548435</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>joon</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>dalba ウォーターフル トーンアップ 日焼け止め グリーン 50ml 少女時代のテヨンガールズデイ ヘリ 日焼け止め</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="b">
+        <v>0</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184548435</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1091918756</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Elim</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>フレッシュクレンジングオイル150ml</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>1844</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="b">
+        <v>0</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1091918756</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1138102881</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Elim</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>[イランイランの香り]ネイチャーシャンプー500ml + タンパク質トリートメント500ml</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Kundal</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>2899</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="b">
+        <v>0</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1138102881</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1141313539</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ozoz</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>マデカクリームタイトリフティング, 50ml, 1個 (ボックス無)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>1570</v>
+      </c>
+      <c r="G221" t="n">
+        <v>2</v>
+      </c>
+      <c r="H221" t="b">
+        <v>0</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141313539</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1197617517</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>msh-labo</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>【公式】メイクキープミストクール(仕上げ用化粧水) 80g／夏のメイク崩れ徹底ガード！うるおいチャージ／ひんやり冷感成分配合　汗・水に強い／メイク直し　肌あれ防ぐ　フィックスミスト クールR2</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>タイムシークレット</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G222" t="n">
+        <v>6</v>
+      </c>
+      <c r="H222" t="b">
+        <v>0</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197617517</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1184552954</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>natural-pharmacy</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>肌をうるおす保湿浸透水バランシング（本体）：120mL 松山油脂 化粧水 セラミド ナイアシンアミド エクトイン インナードライ 混合肌.</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>肌をうるおす保湿スキンケア</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G223" t="n">
+        <v>5</v>
+      </c>
+      <c r="H223" t="b">
+        <v>0</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184552954</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1184552806</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>natural-pharmacy</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>アミノ酸浸透ジェル：150mL 松山油脂 保湿ジェル グリセリンフリー オイルフリー さらさら 毛穴ケア 脂性肌 敏感肌</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Ｍマーク</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G224" t="n">
+        <v>2</v>
+      </c>
+      <c r="H224" t="b">
+        <v>0</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184552806</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>1184552957</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>natural-pharmacy</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>肌をうるおす保湿浸透水モイストリッチ（詰替用）：110mL×【3個】 松山油脂 高保湿化粧水 セラミド ナイアシンアミド とろみ 敏感肌</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>肌をうるおす保湿スキンケア</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>3780</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="b">
+        <v>0</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184552957</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J217"/>
+  <autoFilter ref="A1:J225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J225"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9680,8 +9680,664 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1204892189</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>klavuujapan</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>【うるツヤUVケアセット】日焼け止めジェル SPF50+ PA++++ ＋ 女優下地クリーム 「下地・UV対策・日焼け止め・日焼け対策・BBクリーム」</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>クラビュー</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>2720</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="b">
+        <v>0</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204892189</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1172575457</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>klavuujapan</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>【4個選択可】リップスリーピングパック4種 20g 「リップマスク・リップクリーム・リップバーム・保湿リップ・唇パック・唇ケア・リップパック・リップケア・リップ保湿・保湿リップ」</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>クラビュー</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>5120</v>
+      </c>
+      <c r="G227" t="n">
+        <v>7</v>
+      </c>
+      <c r="H227" t="b">
+        <v>0</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1172575457</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1152076163</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>atrue</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>オリジン カーミング リリーフ クリーム 80ml 2個セット/ 水分クリーム / スクアラン / パンテノール</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>ATRUE</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>2873</v>
+      </c>
+      <c r="G228" t="n">
+        <v>8</v>
+      </c>
+      <c r="H228" t="b">
+        <v>0</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1152076163</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1190357951</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ludiana</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>[国内発送]ヒアルロニックシナジークリーム 50g 正規品 韓国コスメ 保湿 高保湿 ヒアルロニック シナジー クリーム スキンケア 敏感肌 ケア 乾燥肌 保護 フェイスクリーム</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>イアンセル</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>8480</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="b">
+        <v>0</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190357951</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1190357736</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ludiana</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>[国内発送]ヒアルロニックシナジートナー 200ml 正規品 韓国コスメ 保湿 高保湿 ヒアルロニック シナジー トナー スキンケア 敏感肌ケア 乾燥肌ケア 毛穴ケア</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>イアンセル</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>4780</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="b">
+        <v>0</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190357736</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1194385607</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ludiana</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>[国内発送]エコエンナアルガンゴールドモイスチャーボディローション 500ml 正規品 韓国コスメ ボディローション アルガンオイル ゴールド 高保湿 しっとり 保湿 乾燥対策　ボディケア 全身ケア</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ウェルコス</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="b">
+        <v>0</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194385607</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1185182331</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ludiana</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>id EXO-V ブースターアンプル 30ml　韓国ドクターズコスメ　ブースターアンプル　美白　毛穴　シワ改善　乾燥肌　スキンケア　保湿　潤い　エクソゾーム　ナイアシアミド　しっとり　モチモチ</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>id PLACOSMETICS</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="b">
+        <v>0</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185182331</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1188868881</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ludiana</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>[国内発送]インプルーブメラトーニングクリーム 70ml 正規品 韓国コスメ クリーム フェイスクリーム メラトーニング 栄養補給 インプルーブ スキンケア 透明感 弾力 潤い</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>イアンセル</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>7980</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="b">
+        <v>0</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188868881</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1188519198</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>K-beautyclub</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>プラセン スキンシールド リニューアル クリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>ルネセル</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>2780</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="b">
+        <v>0</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188519198</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1119012312</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>K-beautyclub</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>アブソーバー ヒアルロニック セラム 30ml おすすめ商品 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>ルネセル</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>4300</v>
+      </c>
+      <c r="G235" t="n">
+        <v>7</v>
+      </c>
+      <c r="H235" t="b">
+        <v>0</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1119012312</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1185925532</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>K-beautyclub</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>滋陰水 EX 150ml（リニューアル新版）</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>雪花秀</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>4780</v>
+      </c>
+      <c r="G236" t="n">
+        <v>4</v>
+      </c>
+      <c r="H236" t="b">
+        <v>0</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185925532</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>989737949</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>grace0723</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>イェファダム千三輪自生クリーム50ml 韓国コスメ おすすめ商品</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>ザフェイスショップ</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>3589</v>
+      </c>
+      <c r="G237" t="n">
+        <v>5</v>
+      </c>
+      <c r="H237" t="b">
+        <v>0</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=989737949</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1162975495</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>grace0723</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>韓方ヘアシャンプー500ml+ヘアコンディショナー500ml</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Atom美</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>3649</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="b">
+        <v>0</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1162975495</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1203143752</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>seoandahmall1</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>[1+1セット] PDRN スキンブースター サンセラム 50ml SPF50+ PA++++/ UV美容液 / 24時間UVカット/ 保湿 / 低刺激 /日焼け止め / 韓国コスメ/ UVケア /</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>ドクタージー</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>5090</v>
+      </c>
+      <c r="G239" t="n">
+        <v>3</v>
+      </c>
+      <c r="H239" t="b">
+        <v>0</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203143752</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1202799714</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>seoandahmall1</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ティーツリーシカ鎮静トナー 250ml / 500ml 選べる大容量 / 肌荒れケア ティ/ 毛穴 /ニキビケア/ オリーブヤング人気 トナー/ 敏感肌 / 皮脂コントロール /水分 / 保湿 / 韓</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G240" t="n">
+        <v>4</v>
+      </c>
+      <c r="H240" t="b">
+        <v>0</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202799714</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1202710184</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>seoandahmall1</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3日集中鎮静！ジンクテカ トラブルセラム25ml + ティーツリーシカスージングクリームプラス100ml /オリーブヤング人気No.1 トラブルケアセット /敏感インナードライ肌ケア /韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>4780</v>
+      </c>
+      <c r="G241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H241" t="b">
+        <v>0</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202710184</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J225"/>
+  <autoFilter ref="A1:J241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$243</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10336,8 +10336,90 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1164923832</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>cosmeticface</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>[ナンバーズ·イン]ナンバーズイン１番　青い薬草たっぷり93パーセントトナー</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>ナンバーズイン</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>2380</v>
+      </c>
+      <c r="G242" t="n">
+        <v>3</v>
+      </c>
+      <c r="H242" t="b">
+        <v>0</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1164923832</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1149205792</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>cosmeticface</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>クッション/アルティメットカバーメッシュクッション13g*2個</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>オフィ</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>3580</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="b">
+        <v>0</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1149205792</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J241"/>
+  <autoFilter ref="A1:J243"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$247</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J243"/>
+  <dimension ref="A1:J247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10418,8 +10418,172 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1137744862</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>魔女工場ソーダクレンジングフォーム150ml 2個</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>manyo</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="b">
+        <v>0</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1137744862</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1137608208</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>プレステージ トニック 2X デスカルゴスキン140ml 1個</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>イッツスキン</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G245" t="n">
+        <v>6</v>
+      </c>
+      <c r="H245" t="b">
+        <v>0</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1137608208</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1137606600</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>プレステージ ロシオン 2X ジンセン デスカルゴ エマルジョン, 140ml1個</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>イッツスキン</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>3700</v>
+      </c>
+      <c r="G246" t="n">
+        <v>2</v>
+      </c>
+      <c r="H246" t="b">
+        <v>0</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1137606600</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1137606552</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>プレステージ ロシオン 2X ジンセン デスカルゴ エマルジョン, 140ml</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>イッツスキン</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>3700</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="b">
+        <v>0</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1137606552</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J243"/>
+  <autoFilter ref="A1:J247"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$249</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J247"/>
+  <dimension ref="A1:J249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10582,8 +10582,90 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1142392953</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>QQ153</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>グローターン 脱毛ケアアンプル 100ml /ヘアエッセンス/ヘアケア／頭皮ケア／脱毛ケアソリューション</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>lily eve</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>4770</v>
+      </c>
+      <c r="G248" t="n">
+        <v>1</v>
+      </c>
+      <c r="H248" t="b">
+        <v>0</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1142392953</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1187794959</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>QQ153</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>【メガ割対象】パンテノールクリーム 100ml 敏感肌 保湿 肌荒れケア バリアクリーム 韓国スキンケア 乾燥肌 ツヤ肌</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Purito</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>3230</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="b">
+        <v>0</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1187794959</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J247"/>
+  <autoFilter ref="A1:J249"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$260</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J249"/>
+  <dimension ref="A1:J260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10664,8 +10664,459 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1211189584</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>aurelie</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>【Aurelie.公式店】モイスチャーセラムクレンジング MEGUMI開発 クレンジング オイル メイク落とし 化粧落とし しっとり スキンケア 毛穴汚れ 植物性幹細胞</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Aurelie.</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>3960</v>
+      </c>
+      <c r="G250" t="n">
+        <v>2</v>
+      </c>
+      <c r="H250" t="b">
+        <v>0</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211189584</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1192837184</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>aurelie</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>【MEGUMI開発】Aurelie (オレリー) モイストオイル クレンジングウォーター×2wayコットンクレンジング オイル メイク落とし 化粧落とし リムーバー しっとり 毛穴 洗顔 スキンケア</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Aurelie.</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>4290</v>
+      </c>
+      <c r="G251" t="n">
+        <v>2</v>
+      </c>
+      <c r="H251" t="b">
+        <v>0</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1192837184</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1211206466</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>aurelie</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>【Aurelie.公式店】【3本セット】モイストオイル クレンジングウォーター MEGUMI開発 クレンジング オイル メイク落とし 化粧落とし 洗顔 スキンケア 毛穴</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Aurelie.</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>10692</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="b">
+        <v>0</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211206466</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1211201205</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>aurelie</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>【Aurelie.公式店】【3本セット】リンクルリペア セラム 医薬部外品 美容液 保湿 セラム　MEGUMI開発　スキンケア 毛穴 くすみ 美容液 顔 保湿 黒ずみ 低刺激 ブースター アルコー</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Aurelie.</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>23166</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="b">
+        <v>0</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211201205</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1202571743</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>100iromegane</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>スカルプスパ シャンプー 300ml トリートメント 300g 詰替用 頭皮ケア 濃密泡 温冷感スパ処方 ヘアケア 地肌ケア スカルプスパ ボリューム泡</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>レバタ</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>2190</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="b">
+        <v>0</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202571743</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1208581980</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>100iromegane</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>薬用美白 化粧水 詰替用 150ml x 2袋 クラシエ 高純度ビタミンＣ トラネキサム酸 保湿 薬用化粧水 無香料 無着色 アルコールフリー ビタミンC</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>肌美精</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>2180</v>
+      </c>
+      <c r="G255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H255" t="b">
+        <v>0</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208581980</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1207420418</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>100iromegane</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>泡 洗顔料 詰替用 180ml × 3袋 クラシエ 泡 洗顔 洗顔料 スキンケア 敏感肌 着色料 合成香料 無添加 植物オイル 毛穴 毛穴ケア 毛穴汚れ 角質 皮脂 保湿 詰め替え</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>ミュオ</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>1920</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="b">
+        <v>0</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207420418</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1204841344</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>100iromegane</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>スキンライフ 薬用 化粧水 180ml x 2本 牛乳石鹸 無香料 保湿 整肌 殺菌 消炎 ニキビ肌 オイルフリー 医薬部外品</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>スキンライフ</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" t="b">
+        <v>0</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204841344</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1203052107</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>100iromegane</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>洗い流さない ヘアトリートメント ヘアメンテナンス エマルジョン 110mL x 2本 ウテナ ヘアミルク ストレートケア うねり 湿気ブロック ヒートプロテクト フルーティフローラルのの香り</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>PROQUALITE</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>3380</v>
+      </c>
+      <c r="G258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H258" t="b">
+        <v>0</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203052107</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1209841419</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>seoulmate_</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>【スクラブウォッシュ】シュエロ 日本総代理店 ボディスクラブ スクラブ スクラブウォッシュ ボディウォッシュ 角質 黒ずみ 毛穴 コラーゲン 保湿 スキンケア ボディケア 全身ケア</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>SUELO</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="b">
+        <v>0</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209841419</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1209838428</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>seoulmate_</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>【ボディーPPCクリーム】シュエロ 日本総代理店 ボディクリーム ボディー クリーム カッサ かっさ しっとり マッサージ ボディー スキンケア アンプル デイリーケア 韓国 コスメ 韓国スキン 韓国</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>SUELO</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="b">
+        <v>0</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209838428</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J249"/>
+  <autoFilter ref="A1:J260"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$268</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J260"/>
+  <dimension ref="A1:J268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11115,8 +11115,336 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1085152294</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>fujifilm-h</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>ルナメアAC スキンコンディショナー (ノーマルタイプ) 120ml [医薬部外品] アクネケアローション アクネシューター アクネケア 化粧水 ニキビケア ニキビ予防 肌荒れ ノンコメド</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>富士フイルム</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>2684</v>
+      </c>
+      <c r="G261" t="n">
+        <v>2</v>
+      </c>
+      <c r="H261" t="b">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1085152294</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1167420421</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>rebion</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>洗顔フォーム レックスロウウォッシュ 120g 洗顔料 泥 毛穴 50代 40代 濃密泡 泥洗顔料 海シルト 毛穴ケア 毛穴汚れ 黒ずみ 角質ケア 無添加 クレイ洗顔 エイジングケア</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>リビオン</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>2190</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="b">
+        <v>0</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1167420421</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1170385647</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>rebion</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>スキンケア3点セット ヒト幹細胞 保湿 エクソソーム ヒト幹細胞培養液 無添加 ハリ エイジングケア 高保湿 敏感肌 乾燥肌 毛穴 保湿美容液 美肌 潤い 乾燥 化粧水 クリーム</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>リビオン</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>12024</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" t="b">
+        <v>0</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1170385647</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1209049883</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>attenir</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>クレンジング スキンクリア クレンズ オイル 大容量ボトル＆詰め替え用 (ピースフルオレンジの香り) クレンジングオイル メイク落とし 化粧落とし アロマ 毛穴 350ml</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>アテニア</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>3960</v>
+      </c>
+      <c r="G264" t="n">
+        <v>5</v>
+      </c>
+      <c r="H264" t="b">
+        <v>0</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209049883</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>840711749</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Rocoscloset</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ナノEGFセラム アクアイズム EGF 原液美容液 無添加</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>イズム</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="b">
+        <v>0</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=840711749</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1188486332</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>juicetocleanse</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>(公式)[NEW] 抹茶パウダーウォッシュ 50g [酵素洗顔 / 角質ケア / 低刺激 / 韓国コスメ ]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>JUICE TO CLEANSE</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>2496</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="b">
+        <v>0</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188486332</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1152008581</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>juicetocleanse</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>(公式)トーンアップ日焼け止め 50ml [ UVカット / SPF50+ PA++++ / PDRN /ローズカラーのトーンアップ/化粧下地/プライマー/紫外線対策/ 韓国コスメ ]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>JUICE TO CLEANSE</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>2496</v>
+      </c>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="b">
+        <v>0</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1152008581</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1011390974</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>juicetocleanse</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>(公式) ビネガー コンブチャ ヴィーガン クリーム 75ml [ヴィーガン100% / お肌の弾力ケア / コンブチャ35% / 弾力UP 保湿UPGRADE / 植物性コラーゲン配合 ]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>JUICE TO CLEANSE</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>3802</v>
+      </c>
+      <c r="G268" t="n">
+        <v>6</v>
+      </c>
+      <c r="H268" t="b">
+        <v>0</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1011390974</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J260"/>
+  <autoFilter ref="A1:J268"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$269</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J268"/>
+  <dimension ref="A1:J269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11443,8 +11443,49 @@
         </is>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1186954552</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>mixsoonjp</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>ヒアルレベ ポアブラーリングクリーム 50ml 美容液 保湿 毛穴</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>ミクスン</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>2086</v>
+      </c>
+      <c r="G269" t="n">
+        <v>6</v>
+      </c>
+      <c r="H269" t="b">
+        <v>0</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1186954552</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J268"/>
+  <autoFilter ref="A1:J269"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$275</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J269"/>
+  <dimension ref="A1:J275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11484,8 +11484,254 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1128247119</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>happytreemall</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>アルティメット マスク タイム リバース 15 ea</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>ニュースキン</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>8333</v>
+      </c>
+      <c r="G270" t="n">
+        <v>1</v>
+      </c>
+      <c r="H270" t="b">
+        <v>0</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1128247119</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1128246013</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>happytreemall</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>アルティメットマスクウォータープール</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>ニュースキン</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>4568</v>
+      </c>
+      <c r="G271" t="n">
+        <v>2</v>
+      </c>
+      <c r="H271" t="b">
+        <v>0</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1128246013</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1144298674</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>DaisyShop</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>CICA 大容量ライン (化粧水・乳液・クリーム)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G272" t="n">
+        <v>1</v>
+      </c>
+      <c r="H272" t="b">
+        <v>0</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1144298674</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1073380168</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>DaisyShop</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>正規品 セルマン5種オリジナル機能性セット(トナー150ml+セラム30ml+クリーム50ml+ビタミンCセラム30ml+ウォッシュパウダー70g)+/関税なし</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>SERMENT</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>38380</v>
+      </c>
+      <c r="G273" t="n">
+        <v>6</v>
+      </c>
+      <c r="H273" t="b">
+        <v>0</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1073380168</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1169406691</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>DaisyShop</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>ビタミンC グロートニングアンプル 30ml</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>NEEDLY</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>1879</v>
+      </c>
+      <c r="G274" t="n">
+        <v>1</v>
+      </c>
+      <c r="H274" t="b">
+        <v>0</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169406691</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>1095176920</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>DaisyShop</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>[DEOPROCE] カタツムリ リカバリー クリーム 100g</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>ディオプラス</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G275" t="n">
+        <v>5</v>
+      </c>
+      <c r="H275" t="b">
+        <v>0</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1095176920</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J269"/>
+  <autoFilter ref="A1:J275"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$275</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$280</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J275"/>
+  <dimension ref="A1:J280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11730,8 +11730,213 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1169398950</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>pikapikastore</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>No.5 白玉 グルタチオンC ふりかけ マスク/ 韓国コスメ 正規品 おすすめ ビタミンC 栄養集中ケア エイジングケア 弾力 高保湿 美容液 スキンケア 人工色素のない エッセンス</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>ナンバーズイン</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>3399</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1</v>
+      </c>
+      <c r="H276" t="b">
+        <v>0</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169398950</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>1207945805</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>libio</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>PDRN デュアルエッセンス （２本セット）顔・頭皮用ミスト120mL　低刺激設計　ジェンダーフリー</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>libio</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>10692</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" t="b">
+        <v>0</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207945805</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>1207834466</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>libio</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>PDRN デュアルエッセンス 　顔・頭皮用ミスト120mL　低刺激設計　ジェンダーフリー</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>libio</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>5940</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+      <c r="H278" t="b">
+        <v>0</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207834466</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>1189243900</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>yomite</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>【公式】body用(3箱セット)【自宅でハーブピーリング】美容施術 韓国化粧品研究機関共同開発</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>on:myskin</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>16146</v>
+      </c>
+      <c r="G279" t="n">
+        <v>7</v>
+      </c>
+      <c r="H279" t="b">
+        <v>0</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189243900</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>1189190089</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>yomite</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>【公式】デュアルクリーム毛穴 乾燥 くすみ たるみ ハリ弾力 透明感 保湿 高保湿 水光肌 ツヤ肌 バリア機能 韓国スキンケア 集中ケア エイジングケア　ピーリング　ケア　角質　もっちり</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>on:myskin</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>5980</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="b">
+        <v>0</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189190089</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J275"/>
+  <autoFilter ref="A1:J280"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$285</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J280"/>
+  <dimension ref="A1:J285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11935,8 +11935,213 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1191588853</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>alidadashop</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>ピテラ ベスト コレクション トライアル キット 化粧水75mL 美容液10mL クリーム15g スキンケアセット 保湿 透明感 ハリ</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>12649</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" t="b">
+        <v>0</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191588853</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>1202669462</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>alidadashop</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>ジェノプティクス インフィニットオーラ ジェルクリーム 50g</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>18655</v>
+      </c>
+      <c r="G282" t="n">
+        <v>2</v>
+      </c>
+      <c r="H282" t="b">
+        <v>0</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202669462</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>1198647775</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>alidadashop</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>スキンパワー リニュー クリーム 15g 3個セット 美容クリーム 携帯ミニサイズ 保湿 ハリ ふっくら クリア肌</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>8099</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" t="b">
+        <v>0</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198647775</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1206647975</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>doraggunoougoku</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>フィリップス 電動シェーバー 3000Xシリーズ X3051／00 ( 1台 )</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>フィリップス</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="b">
+        <v>0</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206647975</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>1154581392</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>rism-official</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>[公式/日本国内発送] 【2026年夏 福袋】RISM ひんやりスキンケアセット 冷感パック ひんやりパック 日焼けケア</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>RISM</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>3680</v>
+      </c>
+      <c r="G285" t="n">
+        <v>8</v>
+      </c>
+      <c r="H285" t="b">
+        <v>0</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1154581392</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J280"/>
+  <autoFilter ref="A1:J285"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$287</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J285"/>
+  <dimension ref="A1:J287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12140,8 +12140,90 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>1207680190</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>borra-brand</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ボラソフトプロテクトクリームEX PLUS デリケートゾーン ボラソフト 肛門ケア 皮膚を守る 馬油 グリチルレチン酸ステアリル 化粧品 天藤製薬 メガ割 メガポ</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>ボラソフト</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="b">
+        <v>0</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207680190</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>1207003649</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>raughbright</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>洗顔パスタ ホワイトダイヤ 単品 90g</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>ロゼット</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>2060</v>
+      </c>
+      <c r="G287" t="n">
+        <v>2</v>
+      </c>
+      <c r="H287" t="b">
+        <v>0</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207003649</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J285"/>
+  <autoFilter ref="A1:J287"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$293</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J287"/>
+  <dimension ref="A1:J293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12222,8 +12222,254 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>1171256764</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>azabustore</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>【夏のUV・エイジングケアに】クウィーントックス アクアUV サンセラム ＋ セラムパウチ5枚セット 国内配送 公式 日焼け止め 美容液 韓国コスメ 白浮きしない SPF50＋ PA++++</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>QWEENTOX</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>4990</v>
+      </c>
+      <c r="G288" t="n">
+        <v>2</v>
+      </c>
+      <c r="H288" t="b">
+        <v>0</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171256764</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>1203107274</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>azabustore</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>【大人気・夏のインナードライ・砂漠肌ケア】クウィーントックス カプセルバイオクリーム2個＋セラムサンプル3枚 国内配送 公式品 韓国コスメ 保湿 エイジングケア チョウザメ PDRN</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>QWEENTOX</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>14800</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="b">
+        <v>0</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203107274</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>1202232907</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>azabustore</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>【夏の紫外線ダメージ対策に】クウィーントックス バイオブースター美容水2本＋セラムパウチ3枚 セット 国内配送 公式 導入化粧水 トナー 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>QWEENTOX</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1</v>
+      </c>
+      <c r="H290" t="b">
+        <v>0</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202232907</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>1094137657</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>feg-official</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>【FEG公式】 パーフェクトセラム アゼライン酸5%配合 CICA配合 PERFECT SERUM 30ml</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>1699</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" t="b">
+        <v>0</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1094137657</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>1213272505</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>moaseoulshop</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>【正規品】美容液2種セット PDRNヒアルロン酸×ドクダミ カプセル100＋77 B3ジンク 各30ml</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>4580</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="b">
+        <v>0</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213272505</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>1213263295</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>moaseoulshop</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>【正規品】 ピンクセラムセット 桃70ナイアシン 30ml＋ナイアシンアミド10 TXA 30ml</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>4380</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="b">
+        <v>0</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213263295</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J287"/>
+  <autoFilter ref="A1:J293"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J293"/>
+  <dimension ref="A1:J295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12468,8 +12468,90 @@
         </is>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>1130941646</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>vividco2019</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ランバン/ モダン プリンセス オードパルファム90ml1個</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>ランバン</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>9270</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" t="b">
+        <v>0</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1130941646</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1181249745</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>KBCINTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>公式 リードルショット 100/ 300 50ml 3個 4個 5個 毛穴ケア カタン ニードル ショット アンチ エイジング ニードルショット</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Dr.Bargo</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>2999</v>
+      </c>
+      <c r="G295" t="n">
+        <v>7</v>
+      </c>
+      <c r="H295" t="b">
+        <v>0</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1181249745</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J293"/>
+  <autoFilter ref="A1:J295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$302</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J295"/>
+  <dimension ref="A1:J302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12550,8 +12550,295 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>1129475821</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>auc-j-kazu</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>イングリッシュ ペアー＆フリージア コロン 9ml　スプレータイプ　ミニ香水 Jo Malone</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>ジョーマローンロンドン</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>3580</v>
+      </c>
+      <c r="G296" t="n">
+        <v>9</v>
+      </c>
+      <c r="H296" t="b">
+        <v>0</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1129475821</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>1188151379</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>LindsayShop</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>【6個】 モデリングマスクカップパック 28g 4種 (クールティーツリー / ビタミン / コラーゲン / 鎮静薬草)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>LINDSAY</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>2520</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="b">
+        <v>0</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188151379</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1188204329</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>LindsayShop</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>リネチュラル モデリングパック5種（ジッパーバッグ400g）</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>LINDSAY</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G298" t="n">
+        <v>2</v>
+      </c>
+      <c r="H298" t="b">
+        <v>0</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188204329</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1188288008</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>LindsayShop</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>プロパイオティク ハイドロゲル アイパッチ 60枚 (高濃縮100%エッセンスゲル)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>LINDSAY</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="b">
+        <v>0</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188288008</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>1187534997</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>LindsayShop</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ピーエイチソリューション クールティーツリー マスク 300g(24枚)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>LINDSAY</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" t="b">
+        <v>0</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1187534997</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>1206596838</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>rdrd</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>【7/17~31限定セール+購入金額別にスペシャルGIFT】 りんごトナー/セラム 【5/29 Qoo10先行発売】</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>rdrd</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>2199</v>
+      </c>
+      <c r="G301" t="n">
+        <v>2</v>
+      </c>
+      <c r="H301" t="b">
+        <v>0</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206596838</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>1206596451</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>rdrd</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>【7/17~31限定セール+購入金額別にスペシャルGIFT】 ミニセラム 7ml 選べる2＋1セット（各種類1個まで選択可能）【5/29 Qoo10先行発売】</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>rdrd</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G302" t="n">
+        <v>3</v>
+      </c>
+      <c r="H302" t="b">
+        <v>0</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206596451</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J295"/>
+  <autoFilter ref="A1:J302"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$303</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J302"/>
+  <dimension ref="A1:J303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12837,8 +12837,49 @@
         </is>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1171401717</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>siscos</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>[3個セット]パーフェクト マジック ストレート 3点セット(シャンプー530ml+トリートメント230ml+セラム 80ml)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>ミジャンセン</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>7950</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="b">
+        <v>0</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171401717</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J302"/>
+  <autoFilter ref="A1:J303"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$304</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J303"/>
+  <dimension ref="A1:J304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12878,8 +12878,49 @@
         </is>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1161331720</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>miraclim</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>【国内発送】メイク前 パック【1個】VT SKINPACK COOL(ひんやり) (100枚入)【正規品】スキンパック 夏 冷感 クーリング パック 部分用パック 顔 パック シートマスク</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G304" t="n">
+        <v>4</v>
+      </c>
+      <c r="H304" t="b">
+        <v>0</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161331720</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J303"/>
+  <autoFilter ref="A1:J304"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$305</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J304"/>
+  <dimension ref="A1:J305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12919,8 +12919,49 @@
         </is>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1162730377</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>boomnaru</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ダメージヘア用 弱酸性/アシッドシャンプー/大容量1500ml/ビューティーラボ/ヘアケア/韓国</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>PARKJUN BEAUTY LAB</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>3980</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" t="b">
+        <v>0</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1162730377</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J304"/>
+  <autoFilter ref="A1:J305"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$307</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J305"/>
+  <dimension ref="A1:J307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12960,8 +12960,90 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>1193439473</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>watiforskin</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>【選べる12タイプ】マイクロスピキュール＆ボルプロショットクリーム 50ml/グリコール酸・ナイアシンアミド・レチノール・バクチオル・トラネキサム酸・ヒアルロン酸・PDRN配合</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Wati For Skin</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G306" t="n">
+        <v>1</v>
+      </c>
+      <c r="H306" t="b">
+        <v>0</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193439473</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>1193438313</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>watiforskin</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>【選べる導入美容液】マイクロショット100 美容液 30ml 12種/微細針 肌トラブル管理ソリューション / 韓国化粧品/リドルショットコンセプト</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Wati For Skin</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G307" t="n">
+        <v>3</v>
+      </c>
+      <c r="H307" t="b">
+        <v>0</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193438313</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J305"/>
+  <autoFilter ref="A1:J307"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$307</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$320</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J307"/>
+  <dimension ref="A1:J320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13042,8 +13042,541 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>1094120054</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>【日本公式代理店】韓国 アイクリーム レチノコラーゲン低分子300集中クリーム レチノール レチナール 目元たるみ 30代 40代 50代 低分子フィッシュコラーゲン しわ 目尻 ほうれい 人気</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>CKD_GUARANTEED</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" t="b">
+        <v>0</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1094120054</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>1145826907</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>【公式】ウォーターフィット サンセラム 日焼け止め 国内発送 シカ センテラ 韓国コスメ 水分 保湿 鎮静 低刺激 UVカット 化粧下地 紫外線</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" t="b">
+        <v>0</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1145826907</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>1175765151</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>【公式】Vita 3 ACE Aurora Toner 化粧水 保湿 ビタミン インナードライ スキンケア 韓国コスメ 水光肌 トーンアップ ニキビ跡ケア 国内発送</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>オーズナリー</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>2790</v>
+      </c>
+      <c r="G310" t="n">
+        <v>3</v>
+      </c>
+      <c r="H310" t="b">
+        <v>0</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175765151</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1175759418</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>【公式】 【LDK受賞】 Vita 3 BBC Pudding Cream ビタミン 跡ケア 保湿 高密着 スキンケア ナイトケア スリーピングパック トーンアップ</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>オーズナリー</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0</v>
+      </c>
+      <c r="H311" t="b">
+        <v>0</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175759418</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1174265093</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>【公式】 プロバイオシカ インテンシブアンプル アンプル 50ml 美容液 鎮静 保湿 バリア ケア スキンケア センテラ ツボクサ　国内発送</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G312" t="n">
+        <v>4</v>
+      </c>
+      <c r="H312" t="b">
+        <v>0</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1174265093</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>1100332949</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>balifesta</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>サンスクリーン Daily Refreshing Serum SPF50+ PA++++ 170ml 海外直送品</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>ヴァセリン</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>3690</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" t="b">
+        <v>0</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1100332949</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>1208319671</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>balifesta</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Mugwort　Acne Clay Stick　40g</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>SKINTIFIC</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>4990</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" t="b">
+        <v>0</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208319671</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>1208182736</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>balifesta</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>PDRN シリーズ　Radiance Bright Serum Spray　100ml</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>SKINTIFIC</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>5590</v>
+      </c>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" t="b">
+        <v>0</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208182736</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>1191796909</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>lamelin</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>【キメ・しっとり・なめらか】ラメリン ミラクルNMNプラスPDRN バイオトックス クリーム 50ml シワ毛穴ケア(NMN/PDRN)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>LAMELIN</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>3070</v>
+      </c>
+      <c r="G316" t="n">
+        <v>15</v>
+      </c>
+      <c r="H316" t="b">
+        <v>0</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191796909</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1203108437</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>reveam</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>リブエム ウォーターフィット 8重保湿トナーパッド 詰め替え 角質ケア 保湿 30枚</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Reve:am</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>1630</v>
+      </c>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" t="b">
+        <v>0</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203108437</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>1206155481</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>beiskin</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>【ハリ密着】ローズウォーター コラーゲン マスク 500Da 超低分子 10枚入</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>beiskin</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>4980</v>
+      </c>
+      <c r="G318" t="n">
+        <v>3</v>
+      </c>
+      <c r="H318" t="b">
+        <v>0</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206155481</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>1203211333</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>BRMUD_Official</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>【公式】 リカバリーマッドスクラブデイリーウォッシュ 500ml／ボディソープ／ボディウォッシュ／天然泥スクラブ／背中ニキビ／角質ケア／なめらかシルク肌／お風呂</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>BRMUD</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G319" t="n">
+        <v>13</v>
+      </c>
+      <c r="H319" t="b">
+        <v>0</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203211333</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1145867764</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>BRMUD_Official</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>【公式】リリーフマッドマスク200ML／洗い流す泥パック／クレイパック／毛穴・角質ケア／黒ずみ／ピーリング／ニキビケア／皮脂撲滅／ゆでたまご肌</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>BRMUD</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G320" t="n">
+        <v>14</v>
+      </c>
+      <c r="H320" t="b">
+        <v>0</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1145867764</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J307"/>
+  <autoFilter ref="A1:J320"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$334</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J320"/>
+  <dimension ref="A1:J334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13575,8 +13575,582 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>1104732964</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>idplacosmeticsofficial</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>【正規品】　id フェイスフィットSLバンドV2　【10枚セット】　【下あごケア用】　イヤーリングタイプ　マイナスバンド　接着剤無し　100％ハイドロジェル　韓国最大の美容整形外科開発</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>id PLACOSMETICS</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G321" t="n">
+        <v>1</v>
+      </c>
+      <c r="H321" t="b">
+        <v>0</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1104732964</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1184935545</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>tomocos</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>ブダペスト ボディーローション 300ml</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>raconteur</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="b">
+        <v>0</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184935545</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1184934871</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>tomocos</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>バンフ ボディオイル 150ml</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>raconteur</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" t="b">
+        <v>0</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184934871</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1152365470</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>puremax</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ハイエンド SPF50 スパ 日焼け止め 1個</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>LBB</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>4330</v>
+      </c>
+      <c r="G324" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" t="b">
+        <v>0</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1152365470</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>1152911535</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>puremax</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>ー グリーントマト フォア リフティング アンプル 75ml 1個</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Sung Boon Editor</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>2970</v>
+      </c>
+      <c r="G325" t="n">
+        <v>2</v>
+      </c>
+      <c r="H325" t="b">
+        <v>0</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1152911535</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1209815486</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>uiq-japan</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>【新発売】バイオームレメディポアリセットクーリングPDRNハイドロゲルマスク5枚セット #肌クールダウン #毛穴ケア #化粧ノリUP</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>UIQ</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>3090</v>
+      </c>
+      <c r="G326" t="n">
+        <v>7</v>
+      </c>
+      <c r="H326" t="b">
+        <v>0</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209815486</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1170053960</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>mayo</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>プロテイン ダメージケア バイオレット ミュゲの香り / アイリッシュ/イランイラン 3つの香り シャンプー500ml + トリートメント250ml</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Kundal</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>3090</v>
+      </c>
+      <c r="G327" t="n">
+        <v>7</v>
+      </c>
+      <c r="H327" t="b">
+        <v>0</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1170053960</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1211377983</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>GODONSHOP</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>KIEHL’S キールズ レアアース マスク 125mL フェイスマスク</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>キールズ</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>4390</v>
+      </c>
+      <c r="G328" t="n">
+        <v>0</v>
+      </c>
+      <c r="H328" t="b">
+        <v>0</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211377983</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>1208526902</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>GODONSHOP</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>KIEHL’S キールズ クリーム UFC クリーム 125mL 大容量 保湿 クリーム</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>キールズ</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>6190</v>
+      </c>
+      <c r="G329" t="n">
+        <v>0</v>
+      </c>
+      <c r="H329" t="b">
+        <v>0</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208526902</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1211377673</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>GODONSHOP</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>KIEHL’S キールズ DSクリアリーブライト エッセンス 美容液 100ml 115ml</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>キールズ</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>16990</v>
+      </c>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" t="b">
+        <v>0</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211377673</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>984679415</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>beauty_sky</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>round lab 韓国sns話題_白樺水分トナー300ml_韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G331" t="n">
+        <v>6</v>
+      </c>
+      <c r="H331" t="b">
+        <v>0</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=984679415</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>984679124</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>beauty_sky</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>round lab 韓国sns話題_シラカバ水分クリーム80ml_韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>3249</v>
+      </c>
+      <c r="G332" t="n">
+        <v>10</v>
+      </c>
+      <c r="H332" t="b">
+        <v>0</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=984679124</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>1208272693</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>furriky</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>[GIFT SET] ヘアミスト グロー Belle ＆ ピンクファーリー ポーチキーリング</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Furriky</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>5617</v>
+      </c>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" t="b">
+        <v>0</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208272693</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>1211534870</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>seoullife</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ジャムパッククレンザー 120ml</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>earfit</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" t="b">
+        <v>0</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211534870</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J320"/>
+  <autoFilter ref="A1:J334"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$341</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J334"/>
+  <dimension ref="A1:J341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14149,8 +14149,295 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>1205700934</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>whippedofficial</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>【公式】マグツリーヴィーガンパッククレンザー＋マデカソサイド130g[チューブタイプ] 洗顔・クレンジング・スキンケア・毛穴・保湿・角栓・インナードライ・混合肌・敏感肌</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>ホイップド</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>2970</v>
+      </c>
+      <c r="G335" t="n">
+        <v>18</v>
+      </c>
+      <c r="H335" t="b">
+        <v>0</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205700934</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>1200673600</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>kstyle2023</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>【公式】【正規品】【国内発送】The Harnay Cicaide mist【ザ・ハーネイ シカイド ミスト】</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>THE HARNAY</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>2680</v>
+      </c>
+      <c r="G336" t="n">
+        <v>0</v>
+      </c>
+      <c r="H336" t="b">
+        <v>0</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200673600</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>1202407119</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>imama</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>【3個】 ヘアトニック　無香料クールタイプ 240ml×3個 育毛 養毛 促進ふけかゆみ薄毛 正規品保証</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>柳屋</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G337" t="n">
+        <v>0</v>
+      </c>
+      <c r="H337" t="b">
+        <v>0</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202407119</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>1179990006</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>imama</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>【3個】フイーノ プレミアムタッチ 濃厚美容液ハアマスク 230g×3個 正規品</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>フィーノ</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G338" t="n">
+        <v>3</v>
+      </c>
+      <c r="H338" t="b">
+        <v>0</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179990006</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>1075094781</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>aign</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>シルクプロアイロン ラディアント レッド 35mm ヘアアイロン ストレート ストレートアイロン 美容師推奨品 プロ プロ仕様</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>radiant</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>27500</v>
+      </c>
+      <c r="G339" t="n">
+        <v>3</v>
+      </c>
+      <c r="H339" t="b">
+        <v>0</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1075094781</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>1213144274</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>KJSME</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>【国内発送】ディープダメージトリートメントEX 320ml ウォームペタル</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>UNOVE</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G340" t="n">
+        <v>0</v>
+      </c>
+      <c r="H340" t="b">
+        <v>0</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213144274</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>1175638440</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>KJSME</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>【国内発送】 温感ブルーマスク 35g 洗い流すパック フェイスパック</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Torhop</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G341" t="n">
+        <v>0</v>
+      </c>
+      <c r="H341" t="b">
+        <v>0</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175638440</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J334"/>
+  <autoFilter ref="A1:J341"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$343</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J341"/>
+  <dimension ref="A1:J343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14436,8 +14436,90 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>1122735749</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>KSJ</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>【数量限定セール 】ダメージヘアケア2点セット[シャンプー500ml + トリートメント250ml ]ダメージケア</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Kundal</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>2777</v>
+      </c>
+      <c r="G342" t="n">
+        <v>5</v>
+      </c>
+      <c r="H342" t="b">
+        <v>0</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1122735749</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>1141152293</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>KSJ</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>モデリング クリーム マスク 復活草 スクープ 71mL/1個, 2個 選択</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>アビブ</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" t="b">
+        <v>0</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141152293</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J341"/>
+  <autoFilter ref="A1:J343"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$344</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J343"/>
+  <dimension ref="A1:J344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14518,8 +14518,49 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>1121008564</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>smartselect</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>フォーマント シグネチャー コットンスプレー コットンハグ 200ml</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>FORMENT</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>4780</v>
+      </c>
+      <c r="G344" t="n">
+        <v>0</v>
+      </c>
+      <c r="H344" t="b">
+        <v>0</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1121008564</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J343"/>
+  <autoFilter ref="A1:J344"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$344</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$345</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J344"/>
+  <dimension ref="A1:J345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14559,8 +14559,49 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1105987120</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>jmjp</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>ディズニープリンセス ハンドクリーム　フランス専門調香師のプレミアムパフューム</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>JM solution -Japan Editio</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>880</v>
+      </c>
+      <c r="G345" t="n">
+        <v>3</v>
+      </c>
+      <c r="H345" t="b">
+        <v>0</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1105987120</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J344"/>
+  <autoFilter ref="A1:J345"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$345</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$347</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J345"/>
+  <dimension ref="A1:J347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14600,8 +14600,90 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>1173204704</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>suisosum</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>H&amp;amp;［アッシュアンドアシッドヒートトリートメント 酸熱トリートメント 洗い流さないトリートメント ストレートヘア リリージャスミンの香り ダメージ補修 ツヤ出し 速乾 送料無料</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>H＆</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G346" t="n">
+        <v>3</v>
+      </c>
+      <c r="H346" t="b">
+        <v>0</v>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1173204704</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>1138058611</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>suisosum</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>H&amp;amp; パック シートマスク フェイスマスク 30枚 大容量 ナイアシンアミド プロテオグリカン CICA ビタミンC コラーゲン 高保湿 マスク フェイスパック マスクパック スキンケア</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>H＆</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G347" t="n">
+        <v>8</v>
+      </c>
+      <c r="H347" t="b">
+        <v>0</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1138058611</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J345"/>
+  <autoFilter ref="A1:J347"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$350</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J347"/>
+  <dimension ref="A1:J350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14682,8 +14682,131 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1209053534</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Lowlize</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>【公式/新発売】カーミング トラベルキット+(*カート番号ごとに一つ)シャシェ2種</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Lowlize</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>2880</v>
+      </c>
+      <c r="G348" t="n">
+        <v>0</v>
+      </c>
+      <c r="H348" t="b">
+        <v>0</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209053534</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>1205876934</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Lowlize</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>【公式】バランスリカバリーマスク1枚+(*カート番号ごとに一つ)シャシェ2種</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Lowlize</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>378</v>
+      </c>
+      <c r="G349" t="n">
+        <v>7</v>
+      </c>
+      <c r="H349" t="b">
+        <v>0</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205876934</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1200670476</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Lowlize</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>[公式]エアリー デュ サン セラム+(*カート番号ごとに一つ)シャシェ2種</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Lowlize</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>2736</v>
+      </c>
+      <c r="G350" t="n">
+        <v>5</v>
+      </c>
+      <c r="H350" t="b">
+        <v>0</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200670476</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J347"/>
+  <autoFilter ref="A1:J350"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$353</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J350"/>
+  <dimension ref="A1:J353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14805,8 +14805,131 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1099343162</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>sopo</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>【夏のヘアケア福袋】by Yarden バイヤーデン ダメージケア シャンプー2個&amp;amp;トリートメント2個&amp;amp;スカルプリリーフセラムセット</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>by yarden</t>
+        </is>
+      </c>
+      <c r="F351" t="n">
+        <v>4284</v>
+      </c>
+      <c r="G351" t="n">
+        <v>3</v>
+      </c>
+      <c r="H351" t="b">
+        <v>0</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1099343162</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>1200195801</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>sopo</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>【ダメージケア】by Yarden バイヤーデン ダメージケア ダメージヘア 補修 シャンプー&amp;amp;トリートメント</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>by yarden</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G352" t="n">
+        <v>9</v>
+      </c>
+      <c r="H352" t="b">
+        <v>0</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200195801</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>1201956239</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>sopo</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>【ヘアセラム】by Yarden バイヤーデン スカルプ リリーフ セラム</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>by yarden</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G353" t="n">
+        <v>0</v>
+      </c>
+      <c r="H353" t="b">
+        <v>0</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201956239</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J350"/>
+  <autoFilter ref="A1:J353"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$353</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$358</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J353"/>
+  <dimension ref="A1:J358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14928,8 +14928,213 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>1203847132</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>hairtheory-lab</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>【公式】【べスコス多数受賞】ヘアセオリーラボ フューチャー バイタル エッセンス / 50mL / 正規品 / 頭皮美容液 スカルプケア 頭皮ケア ボリュームケア ハリ コシ エイジングケア 美髪</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Hair Theory Lab</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>7920</v>
+      </c>
+      <c r="G354" t="n">
+        <v>1</v>
+      </c>
+      <c r="H354" t="b">
+        <v>0</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203847132</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>1191440176</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>hairtheory-lab</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>【公式】ヘアセオリーラボ セラムイン オイル アウトバストリートメント / 95ml / Hair Theory Lab 正規品 / 洗い流さないトリートメント アウトバスヘアケア ダメージケア</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Hair Theory Lab</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>5940</v>
+      </c>
+      <c r="G355" t="n">
+        <v>16</v>
+      </c>
+      <c r="H355" t="b">
+        <v>0</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191440176</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>1156253951</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>hairtheory-lab</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>【公式】ヘアセオリーラボ セラムイン トリートメント / 300ml / 正規品 / うねり くせ毛 パサつき 乾燥 ダメージケア ハリ コシ ツヤ 輝き うるおい まとまり 美容液</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Hair Theory Lab</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G356" t="n">
+        <v>3</v>
+      </c>
+      <c r="H356" t="b">
+        <v>0</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1156253951</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>1156248781</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>hairtheory-lab</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>【公式】ヘアセオリーラボ セラムイン シャンプー / 300ml / 正規品 / うねり くせ毛 パサつき 乾燥 ダメージケア ハリ コシ ツヤ 輝き うるおい まとまり 美容液</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Hair Theory Lab</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>5060</v>
+      </c>
+      <c r="G357" t="n">
+        <v>5</v>
+      </c>
+      <c r="H357" t="b">
+        <v>0</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1156248781</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1139722127</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>beans</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>エッセンスＶ シャンプー 1000ml</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>イオニート</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G358" t="n">
+        <v>12</v>
+      </c>
+      <c r="H358" t="b">
+        <v>0</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1139722127</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J353"/>
+  <autoFilter ref="A1:J358"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$358</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$363</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J358"/>
+  <dimension ref="A1:J363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15133,8 +15133,213 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1123207291</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>cleosbeaute</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>クレオズ ディープモイスチャーヘアミルク 洗い流さないトリートメント 80ml</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Cleo's Beauté</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G359" t="n">
+        <v>19</v>
+      </c>
+      <c r="H359" t="b">
+        <v>0</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1123207291</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>1119235494</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>cleosbeaute</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>マルチダメージリペアオイル　お試し用2ml</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Cleo's Beauté</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>480</v>
+      </c>
+      <c r="G360" t="n">
+        <v>2</v>
+      </c>
+      <c r="H360" t="b">
+        <v>0</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1119235494</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>1199682992</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>ricocell_official</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>済州アロエ ピュアスージングジェル 1000ml</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Ricocell</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G361" t="n">
+        <v>0</v>
+      </c>
+      <c r="H361" t="b">
+        <v>0</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199682992</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1199683408</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ricocell_official</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>済州アロエ ピュアスージングジェル 150ml</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Ricocell</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>700</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="b">
+        <v>0</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199683408</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1152006526</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>ricocell_official</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>ネイチャー リカバリー マスクパック 23g 10枚</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Ricocell</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" t="b">
+        <v>0</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1152006526</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J358"/>
+  <autoFilter ref="A1:J363"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$366</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J363"/>
+  <dimension ref="A1:J366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15338,8 +15338,131 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1190007692</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>bespoir</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>peau de Reve（ポードレーヴ） トリプルVCローション 100mL＋MOUクリーム 50g 日本製 セラミド ビタミンC 誘導体 アラントイン ナイアシンアミド うるおい 化粧水 クリーム</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>peau de Reve</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>9450</v>
+      </c>
+      <c r="G364" t="n">
+        <v>1</v>
+      </c>
+      <c r="H364" t="b">
+        <v>0</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190007692</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1188455744</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>bespoir</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>peau de Reve（ポードレーヴ） MOUクリーム 50g 日本製 クリーム セラミド ガラクトミセス グリチルリチン酸 トコフェリルリン酸 うるおい 顔 フェイシャル スキンケア 保湿 乾燥</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>peau de Reve</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>2970</v>
+      </c>
+      <c r="G365" t="n">
+        <v>2</v>
+      </c>
+      <c r="H365" t="b">
+        <v>0</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188455744</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1188455621</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>bespoir</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>peau de Reve（ポードレーヴ）トリプルVCローション 100mL 日本製 化粧水 ビタミンC 誘導体 ナイアシンアミド アラントイン うるおい</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>peau de Reve</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>6980</v>
+      </c>
+      <c r="G366" t="n">
+        <v>1</v>
+      </c>
+      <c r="H366" t="b">
+        <v>0</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188455621</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J363"/>
+  <autoFilter ref="A1:J366"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$367</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J366"/>
+  <dimension ref="A1:J367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15461,8 +15461,49 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1206612215</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Daewoong_Qoo10_Official</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>【公式】TARAJU 4点セット（パッククレンザー150ml＋VCトナー150ml＋リペアライン2種orVCラディアントライン2種）</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>TARAJU</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>6178</v>
+      </c>
+      <c r="G367" t="n">
+        <v>6</v>
+      </c>
+      <c r="H367" t="b">
+        <v>0</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206612215</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J366"/>
+  <autoFilter ref="A1:J367"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$367</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$373</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J367"/>
+  <dimension ref="A1:J373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15502,8 +15502,254 @@
         </is>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1194182321</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>supershinylobh</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>肌荒れ 赤みケア 高保湿ジェル 敏感肌 低刺激 保湿ジェル うるおいケア プロポリス配合 韓国スキンケア</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Super Shiny Lobh</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G368" t="n">
+        <v>17</v>
+      </c>
+      <c r="H368" t="b">
+        <v>0</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194182321</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>1208402960</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>hemille</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>キム・ソヒョン院長/本草/麹高保湿クリーム/ガラクトミセス培養液50g</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>HEMILLE</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>3940</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" t="b">
+        <v>0</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208402960</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>1159799534</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>hemille</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>韓国トーンアップ日焼け止めクリーム uvケア/ナチュラルな陶器肌演出 韓方伝統サンケアコスメ [キム・ソヒョン院長の開発]/30ml x 2個</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>HEMILLE</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>3530</v>
+      </c>
+      <c r="G370" t="n">
+        <v>1</v>
+      </c>
+      <c r="H370" t="b">
+        <v>0</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159799534</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1209204007</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>hemille</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>キム・ソヒョン院長/発酵麹/ クレンジング/洗顔石けん2本</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>HEMILLE</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>3160</v>
+      </c>
+      <c r="G371" t="n">
+        <v>0</v>
+      </c>
+      <c r="H371" t="b">
+        <v>0</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209204007</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>1197856944</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>hemille</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>キム・ソヒョン院長/脱毛症状緩和/本草/スカルプシャンプー500ml2本</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>HEMILLE</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>5520</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" t="b">
+        <v>0</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197856944</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1197325826</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>hemille</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>キム・ソヒョン院長/本草エキス/白髪染め/1剤・2剤同時吐出/ヴィーガン認証/ハリ・コシダークブラウン200ml</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>HEMILLE</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" t="b">
+        <v>0</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197325826</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J367"/>
+  <autoFilter ref="A1:J373"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$374</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J373"/>
+  <dimension ref="A1:J374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15748,8 +15748,49 @@
         </is>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1211563028</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>dotstore</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>デリケートゾーン ソープ VIO フェムケア デリケートゾーンケア 匂い 臭い におい 黒ずみ 保湿 かゆみ 石鹸 消臭 更年期 無香料 弱酸性 敏感肌 泡タイプ 日本製 150ml</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>dot.</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>2784</v>
+      </c>
+      <c r="G374" t="n">
+        <v>1</v>
+      </c>
+      <c r="H374" t="b">
+        <v>0</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211563028</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J373"/>
+  <autoFilter ref="A1:J374"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$375</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J374"/>
+  <dimension ref="A1:J375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15789,8 +15789,49 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1138462623</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>natubeaute</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>洗顔 泥 どろばーゆ 泡洗顔 120g 洗顔フォーム 洗顔料 毛穴汚れ クレイ洗顔 炭 海シルト 馬油 無香料 ローズの香り つっぱりにくい 日本製 女性 メンズ</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>ナチュボーテ</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>1540</v>
+      </c>
+      <c r="G375" t="n">
+        <v>1</v>
+      </c>
+      <c r="H375" t="b">
+        <v>0</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1138462623</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J374"/>
+  <autoFilter ref="A1:J375"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$376</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J375"/>
+  <dimension ref="A1:J376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15830,8 +15830,49 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>1207645599</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>whiteconc</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>【数量限定】薬用ホワイト ニングCC Cll 200ｇ シナモロール限定デザイン ／ CCクリーム 全身用 顔用 グレープフルーツの香り 保湿 トーンアップ 医薬部外品</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>ホワイトコンク</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>1210</v>
+      </c>
+      <c r="G376" t="n">
+        <v>3</v>
+      </c>
+      <c r="H376" t="b">
+        <v>0</v>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207645599</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J375"/>
+  <autoFilter ref="A1:J376"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$377</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J376"/>
+  <dimension ref="A1:J377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15871,8 +15871,49 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1198755469</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>kiwiglow</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>ビーガンジェジュ 蓮マイルド角質ケアトナーパッド</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>KIWIGLOW</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G377" t="n">
+        <v>1</v>
+      </c>
+      <c r="H377" t="b">
+        <v>0</v>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198755469</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J376"/>
+  <autoFilter ref="A1:J377"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$377</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$378</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J377"/>
+  <dimension ref="A1:J378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15912,8 +15912,49 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1044468382</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>raftelcosmetic</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>【公式】インテンシブ PM 10 セラム 30ml シワ 夜用 美容液 高濃縮 弾力 抗酸化 ナイアシンアミド スクアラン ヒアルロン酸</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>RAFTEL</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>7300</v>
+      </c>
+      <c r="G378" t="n">
+        <v>15</v>
+      </c>
+      <c r="H378" t="b">
+        <v>0</v>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1044468382</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J377"/>
+  <autoFilter ref="A1:J378"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$382</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J378"/>
+  <dimension ref="A1:J382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15953,8 +15953,172 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1207551990</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>refindbeauty</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>1000円ぽっきり【選べる3シート】エリップス カカオフレンズ ヘアビタミン シートタイプ 8粒 ヘアオイル 洗い流さないトリートメント ダメージケア 保湿 カラーケア アピーチ ライアン チュン</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>エリップス</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+      <c r="H379" t="b">
+        <v>0</v>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207551990</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>1207659001</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>refindbeauty</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>【選べる3本セット】エリップス カカオフレンズ ヘアオイル ポンプタイプ 95ml 洗い流さないトリートメント ヘアビタミン ダメージケア 保湿 カラーケア アピーチ ライアン チュンシク</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>エリップス</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G380" t="n">
+        <v>0</v>
+      </c>
+      <c r="H380" t="b">
+        <v>0</v>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207659001</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1207558039</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>refindbeauty</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>エリップス カカオフレンズ ヘアオイル ポンプタイプ 95ml 洗い流さないトリートメント ヘアビタミン ダメージケア 保湿 カラーケア アピーチ ライアン チュンシク</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>エリップス</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H381" t="b">
+        <v>0</v>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207558039</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>1203932524</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>refindbeauty</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>i-sam アゼライン酸 洗顔フォーム 150ｇ</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>i-SAMU</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>980</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
+      <c r="H382" t="b">
+        <v>0</v>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203932524</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J378"/>
+  <autoFilter ref="A1:J382"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$382</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$384</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J382"/>
+  <dimension ref="A1:J384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16117,8 +16117,90 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>1160161025</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ecocoslab</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Te パラン10 ( ブルー10) 本体 日焼けオイル/ サンオイル/ ブロンズ肌/ 自然な日焼け/ オイルタイプ/ べたつきなし</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>ｔｅ’</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>4315</v>
+      </c>
+      <c r="G383" t="n">
+        <v>3</v>
+      </c>
+      <c r="H383" t="b">
+        <v>0</v>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1160161025</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>1160148022</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ecocoslab</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>【本品+詰め替えセット】本品/単品から選択 Te チョロク35 (みどり35) サンクッション SPF35+ PA++ 無機日焼け止め 韓国コスメ ナチュラルなトーンアップ 日焼け止め UVケア</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>ｔｅ’</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>5254</v>
+      </c>
+      <c r="G384" t="n">
+        <v>2</v>
+      </c>
+      <c r="H384" t="b">
+        <v>0</v>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1160148022</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J382"/>
+  <autoFilter ref="A1:J384"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$384</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$388</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J384"/>
+  <dimension ref="A1:J388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16199,8 +16199,172 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>1180302383</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>coaplus</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>【公式】コアプレミアムケアミルク　100g　乾燥毛　ダメージケア　保湿　ヘアケア　美容室　銀座　サロン専売品　乳液</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>COA PLUS</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G385" t="n">
+        <v>10</v>
+      </c>
+      <c r="H385" t="b">
+        <v>0</v>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180302383</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>1180301243</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>coaplus</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>【公式】コアプレミアムケアオイル 100ml　【ボトルサイズ】</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>COA PLUS</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G386" t="n">
+        <v>5</v>
+      </c>
+      <c r="H386" t="b">
+        <v>0</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180301243</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>1169290424</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>coaplus</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>【公式】プレミアムケアセラミスト 1000mL　リフィルサイズ　/　ヘアケア　保湿　ダメージケア　美容</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>COA PLUS</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G387" t="n">
+        <v>1</v>
+      </c>
+      <c r="H387" t="b">
+        <v>0</v>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169290424</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>1138054730</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>coaplus</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>【公式】レブ3システムトリートメント 50g</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>COA PLUS</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H388" t="b">
+        <v>0</v>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1138054730</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J384"/>
+  <autoFilter ref="A1:J388"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$388</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$392</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J388"/>
+  <dimension ref="A1:J392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16363,8 +16363,172 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>1159849024</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>skym-store</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>ヴァリジョア シャンプー 300ml + トリートメント 230g セット サロン専売品</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>ディアテック</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>3480</v>
+      </c>
+      <c r="G389" t="n">
+        <v>11</v>
+      </c>
+      <c r="H389" t="b">
+        <v>0</v>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159849024</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>1175522511</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>skym-store</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>スカルプブラシ ワールドプレミアム ロング ゴールド 頭皮ケア</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>エス・ハート・エス</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G390" t="n">
+        <v>2</v>
+      </c>
+      <c r="H390" t="b">
+        <v>0</v>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175522511</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1164523402</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>skym-store</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>【3袋セット】 Varijoie ヴァリジョア シャンプー 10ml + トリートメント 10g セット サシェ サロン専売品 お試し トライアル トラベル</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>ディアテック</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>900</v>
+      </c>
+      <c r="G391" t="n">
+        <v>1</v>
+      </c>
+      <c r="H391" t="b">
+        <v>0</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1164523402</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>1161363897</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>skym-store</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>ビーエックス mm ミリ ワックスフォーム 180g スタイリング ウェーブ キープ パーマ シトラスフローラルの香り b-ex 正規品 サロン専売品</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>モルトベーネ</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G392" t="n">
+        <v>0</v>
+      </c>
+      <c r="H392" t="b">
+        <v>0</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161363897</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J388"/>
+  <autoFilter ref="A1:J392"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$393</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J392"/>
+  <dimension ref="A1:J393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16527,8 +16527,49 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>1146799243</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>paiged</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>【ハリ・弾力×低刺激】溶ける密着フィルム コラーゲンパック 1EA / 低分子コラーゲン / 密着ラップ / 毛穴ケア / 肌弾力・ハリ改善</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Paiged</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H393" t="b">
+        <v>0</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1146799243</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J392"/>
+  <autoFilter ref="A1:J393"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$394</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J393"/>
+  <dimension ref="A1:J394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16568,8 +16568,49 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>617145348</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>39mitsuya</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>VIVANTJOIE JE３０８ 薬用オウゴンジェル 52g</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>VIVANT JOIE</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>13200</v>
+      </c>
+      <c r="G394" t="n">
+        <v>3</v>
+      </c>
+      <c r="H394" t="b">
+        <v>0</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=617145348</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J393"/>
+  <autoFilter ref="A1:J394"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$394</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$398</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J394"/>
+  <dimension ref="A1:J398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16609,8 +16609,172 @@
         </is>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>1186811203</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>azabucosme</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>原液 アゼライン酸 国内最高濃度30％配合 マテリオ materio 20ml アゼライン酸誘導体 生アゼライン酸 部分美容液 メイク崩れ 肌荒れ ゆらぎ肌ケア 毛穴ケア 皮脂ケア ニキビ テカリ</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>AZABU COSMETICS</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G395" t="n">
+        <v>4</v>
+      </c>
+      <c r="H395" t="b">
+        <v>0</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1186811203</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>1194479518</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>azabucosme</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>【薬用男性用育毛剤】 頭頂部・つむじの薄毛（AGA／男性型脱毛症）に効果的な育毛剤 リデンシル配合 ボスケージ 120ml 発毛促進 発毛剤 ボリュームアップ 抜け毛予防 増毛 ハリ コシ 薄毛</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>AZABU COSMETICS</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>3980</v>
+      </c>
+      <c r="G396" t="n">
+        <v>2</v>
+      </c>
+      <c r="H396" t="b">
+        <v>0</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194479518</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>1169292006</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>azabucosme</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>【薬用ノンアルコール育毛剤】 女性用育毛剤 スカルプははこプレミアム 120ml リデンシル配合 ノンアルコール アルコール0％ アルコールフリー ボリュームアップ 発毛剤</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>AZABU COSMETICS</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>5980</v>
+      </c>
+      <c r="G397" t="n">
+        <v>2</v>
+      </c>
+      <c r="H397" t="b">
+        <v>0</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169292006</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>971975274</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>azabucosme</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>【薬用女性用ノンアルコール育毛剤】 スカルプははこ 120ml 発毛 育毛 ボリュームアップ アルコール0％ アルコールフリー 低刺激 保湿成分配合 女性 レディース 発毛剤 育毛剤</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>AZABU COSMETICS</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>3980</v>
+      </c>
+      <c r="G398" t="n">
+        <v>13</v>
+      </c>
+      <c r="H398" t="b">
+        <v>0</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=971975274</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J394"/>
+  <autoFilter ref="A1:J398"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$400</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J398"/>
+  <dimension ref="A1:J400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16773,8 +16773,90 @@
         </is>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>1213385409</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>edelground</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>【オプション付き】シャンプーバー +ボディーバー 固形石鹸 韓国化粧品 頭皮ケア エコー 角質ケア 背中ニキビ</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>edelground</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>2221</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="b">
+        <v>0</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213385409</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>1210959203</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>edelground</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>レッドソルト シャンプーバー 固形シャンプー 韓国化粧品 頭皮ケア エコー シャンプーバー</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>edelground</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>1995</v>
+      </c>
+      <c r="G400" t="n">
+        <v>0</v>
+      </c>
+      <c r="H400" t="b">
+        <v>0</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210959203</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J398"/>
+  <autoFilter ref="A1:J400"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$400</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$402</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J400"/>
+  <dimension ref="A1:J402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16855,8 +16855,90 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>1183479873</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>agea</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>【ageaCream 200ml】 りんご幹細胞トリートメント りんご幹細胞ヘアミルク ブリーチ ダメージ 保湿 サロンケア エイジングケア ダメージケア ヘアケア 髪質改善 洗い流さない アウトバス</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>agea</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>3850</v>
+      </c>
+      <c r="G401" t="n">
+        <v>11</v>
+      </c>
+      <c r="H401" t="b">
+        <v>0</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1183479873</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>1159788922</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>agea</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>【美容師の声から生まれた】 ageaLotionヘアミスト150ml りんご幹細胞ミスト トリートメント リポソーム エイジングケア アウトバストリートメント 洗い流さない ダメージケア スキンケア</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>agea</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>3850</v>
+      </c>
+      <c r="G402" t="n">
+        <v>8</v>
+      </c>
+      <c r="H402" t="b">
+        <v>0</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159788922</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J400"/>
+  <autoFilter ref="A1:J402"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$405</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J402"/>
+  <dimension ref="A1:J405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16937,8 +16937,131 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>1200330416</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>lavieshop</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>シャンプー 400mL &amp;amp; トリートメント 400mL (セット) 詰め替え用</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>ARGANSPA</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>3980</v>
+      </c>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" t="b">
+        <v>0</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200330416</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>855780509</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>youtokyo</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>公式ストア YOUTOKYO シャンプー2本セット（パッションフルーツ） アミノ酸シャンプー 毛髪診断士監修 くせ毛 パサつき 太い髪 アミノ酸 頭皮に優しい ダメージケア 人気</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>ユートーキョー</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>5480</v>
+      </c>
+      <c r="G404" t="n">
+        <v>0</v>
+      </c>
+      <c r="H404" t="b">
+        <v>0</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=855780509</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>855780097</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>youtokyo</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>YOUTOKYO トリートメント 1本（パッションフルーツ）保湿トリートメント 毛髪診断士監修 くせ毛 パサつき 太い髪 広がり ダメージケア 人気 公式ストア まとまる</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>ユートーキョー</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G405" t="n">
+        <v>3</v>
+      </c>
+      <c r="H405" t="b">
+        <v>0</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=855780097</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J402"/>
+  <autoFilter ref="A1:J405"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$405</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$407</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J405"/>
+  <dimension ref="A1:J407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17060,8 +17060,90 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>1211293194</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>plaplaqoo10</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>MO 120ml</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>エルジューダ</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>2244</v>
+      </c>
+      <c r="G406" t="n">
+        <v>0</v>
+      </c>
+      <c r="H406" t="b">
+        <v>0</v>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211293194</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1211290808</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>plaplaqoo10</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>FO 120ml</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>エルジューダ</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>2244</v>
+      </c>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="b">
+        <v>0</v>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211290808</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J405"/>
+  <autoFilter ref="A1:J407"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$409</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J407"/>
+  <dimension ref="A1:J409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17142,8 +17142,90 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>789542280</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Lesthemo</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>CG　リキッド　1週間分サンプル</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>レステモ</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>520</v>
+      </c>
+      <c r="G408" t="n">
+        <v>5</v>
+      </c>
+      <c r="H408" t="b">
+        <v>0</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=789542280</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>602887874</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Lesthemo</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>薬用　美白　ゲルクリーム　1週間分サンプル</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>レステモ</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>500</v>
+      </c>
+      <c r="G409" t="n">
+        <v>11</v>
+      </c>
+      <c r="H409" t="b">
+        <v>0</v>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=602887874</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J407"/>
+  <autoFilter ref="A1:J409"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$409</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$410</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J409"/>
+  <dimension ref="A1:J410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17224,8 +17224,49 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>1189061208</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>kbeauty_flexcos</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>【スペシャルスペシャルプライス】【選べる1＋1】大容量36枚入りパック　デイリーマスクパック（セラミド・レチノール）　パック　マスクパック　保湿　毛穴　スキンケア　在庫処分　ぽっきり　セー</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Flexcos</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G410" t="n">
+        <v>1</v>
+      </c>
+      <c r="H410" t="b">
+        <v>0</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189061208</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J409"/>
+  <autoFilter ref="A1:J410"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$410</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$411</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J410"/>
+  <dimension ref="A1:J411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17265,8 +17265,49 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>917884684</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>francfan</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>クオレ AXI 薬用 サイトプラインMX 200ml 送料無料 ハリコシ 脱毛防止 フケ かゆみ 育</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>クオレ</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>6930</v>
+      </c>
+      <c r="G411" t="n">
+        <v>7</v>
+      </c>
+      <c r="H411" t="b">
+        <v>0</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=917884684</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J410"/>
+  <autoFilter ref="A1:J411"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_10.xlsx
+++ b/output/discovery_result_10.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$411</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$412</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J411"/>
+  <dimension ref="A1:J412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17306,8 +17306,49 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>1203828339</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>STAR-ONLINE</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>【美容皮膚科医 監修】デリケートゾーンケア オイル 120ml フェムケア ボディオイル 保湿 膣 乾燥 黒ずみ くすみ 臭い マッサージ 更年期 閉経 かゆみ 産後 会陰 陰部 VIO バスト</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>CHILL CHER</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G412" t="n">
+        <v>6</v>
+      </c>
+      <c r="H412" t="b">
+        <v>0</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203828339</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J411"/>
+  <autoFilter ref="A1:J412"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>